--- a/data/inflation_2025.xlsx
+++ b/data/inflation_2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alumni-my.sharepoint.com/personal/wrc938_ku_dk/Documents/PhD/1. Projects/1. Estimating output gaps/The-Output-Gap-Does-Not-Exist-1/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alumni-my.sharepoint.com/personal/wrc938_ku_dk/Documents/PhD/1. Projects/1. Estimating output gaps/The-Output-Gap-Does-Not-Exist - rational/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="11_3ACF3EA9956BB3D912E271B64941EEB17DD07FDB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D4CED5E-E097-4E75-800F-AC005FCBD00D}"/>
+  <xr:revisionPtr revIDLastSave="74" documentId="11_3ACF3EA9956BB3D912E271B64941EEB17DD07FDB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4BAC6B15-4172-4BAF-8745-AF13D899D0D2}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="quarterly" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="254">
   <si>
     <t>19841 *Q</t>
   </si>
@@ -778,25 +778,68 @@
   </si>
   <si>
     <t>SPF</t>
+  </si>
+  <si>
+    <t>EXPINF10YR</t>
+  </si>
+  <si>
+    <t>Cleveland 10 year ifnaltion expectation</t>
+  </si>
+  <si>
+    <t>Federal reserve bank of Cleveland</t>
+  </si>
+  <si>
+    <t>Cleveland 1 year ifnaltion expectation</t>
+  </si>
+  <si>
+    <t>EXPINF1YR</t>
+  </si>
+  <si>
+    <t>EXPINF30YR</t>
+  </si>
+  <si>
+    <t>Cleveland 30 year ifnaltion expectation</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="dd/mm/yy"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="170" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="171" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="168" formatCode="0.00000000"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -831,6 +874,11 @@
       <color rgb="FF000000"/>
       <name val="ITC Bookman"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Roboto"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -858,34 +906,45 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="170" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="8" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="4" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="5" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="6" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{E2EBB8E3-5A58-4B8D-88FF-9074B6345018}"/>
     <cellStyle name="Normal 3" xfId="2" xr:uid="{62466D2E-0992-4E1A-9B31-11DA73784E38}"/>
     <cellStyle name="Normal 4" xfId="3" xr:uid="{1E772229-F070-4328-B1FD-DEE862B358F2}"/>
+    <cellStyle name="Normal 5" xfId="4" xr:uid="{F1D117DF-ABD5-4CA2-B0FE-EEBA9A1DC799}"/>
+    <cellStyle name="Normal 6" xfId="5" xr:uid="{7BD36A98-9157-4FF0-9477-2F11228F7372}"/>
+    <cellStyle name="Normal 7" xfId="6" xr:uid="{E1B7E866-1133-4E60-B3DB-467B46A00E29}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1221,7 +1280,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J185"/>
+  <dimension ref="A1:M185"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="8.875" customWidth="1"/>
@@ -1234,10 +1293,13 @@
     <col min="8" max="8" width="69.875" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="52.25" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="58" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="1025" width="8.875" customWidth="1"/>
+    <col min="11" max="11" width="13" customWidth="1"/>
+    <col min="12" max="12" width="11.875" customWidth="1"/>
+    <col min="13" max="13" width="15.875" customWidth="1"/>
+    <col min="14" max="1025" width="8.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:13" ht="31.5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1268,8 +1330,17 @@
       <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="M1" s="11" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1297,8 +1368,17 @@
       <c r="J2" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:10">
+      <c r="K2" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -1327,7 +1407,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:13">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -1356,7 +1436,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:13">
       <c r="A5" t="s">
         <v>32</v>
       </c>
@@ -1385,7 +1465,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:13">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -1413,8 +1493,17 @@
       <c r="J6" s="2" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="7" spans="1:10">
+      <c r="K6" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" t="s">
         <v>44</v>
       </c>
@@ -1442,8 +1531,17 @@
       <c r="J7" s="2" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="8" spans="1:10">
+      <c r="K7" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" t="s">
         <v>47</v>
       </c>
@@ -1472,7 +1570,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:13">
       <c r="A9" t="s">
         <v>54</v>
       </c>
@@ -1501,7 +1599,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:13">
       <c r="A10" t="s">
         <v>57</v>
       </c>
@@ -1530,7 +1628,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:13">
       <c r="A11" t="s">
         <v>62</v>
       </c>
@@ -1559,7 +1657,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:13">
       <c r="A12" t="s">
         <v>70</v>
       </c>
@@ -1588,7 +1686,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:13">
       <c r="A13" t="s">
         <v>76</v>
       </c>
@@ -1617,7 +1715,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:13">
       <c r="A14" t="s">
         <v>78</v>
       </c>
@@ -1646,7 +1744,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:13">
       <c r="A15" t="s">
         <v>81</v>
       </c>
@@ -1675,7 +1773,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:13">
       <c r="A16" t="s">
         <v>88</v>
       </c>
@@ -1704,7 +1802,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:13">
       <c r="A17" t="s">
         <v>95</v>
       </c>
@@ -1732,8 +1830,17 @@
       <c r="J17" s="2" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="18" spans="1:10">
+      <c r="K17">
+        <v>111</v>
+      </c>
+      <c r="L17">
+        <v>111</v>
+      </c>
+      <c r="M17">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" t="s">
         <v>97</v>
       </c>
@@ -1761,8 +1868,17 @@
       <c r="J18" s="2" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="19" spans="1:10">
+      <c r="K18" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" t="s">
         <v>99</v>
       </c>
@@ -1781,7 +1897,7 @@
       <c r="F19" s="8">
         <v>30.199000000000002</v>
       </c>
-      <c r="G19" s="9">
+      <c r="G19" s="7">
         <v>4.5999999999999996</v>
       </c>
       <c r="H19" s="2">
@@ -1790,11 +1906,20 @@
       <c r="I19" s="2">
         <v>3.3</v>
       </c>
-      <c r="J19" s="10">
+      <c r="J19" s="9">
         <v>4.9774000000000003</v>
       </c>
-    </row>
-    <row r="20" spans="1:10">
+      <c r="K19" s="10">
+        <v>5.0906632299999997</v>
+      </c>
+      <c r="L19" s="12">
+        <v>5.0466915700000001</v>
+      </c>
+      <c r="M19" s="13">
+        <v>4.3432276700000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" t="s">
         <v>100</v>
       </c>
@@ -1813,7 +1938,7 @@
       <c r="F20" s="8">
         <v>30.367999999999999</v>
       </c>
-      <c r="G20" s="9">
+      <c r="G20" s="7">
         <v>4.4000000000000004</v>
       </c>
       <c r="H20" s="2">
@@ -1822,11 +1947,20 @@
       <c r="I20" s="2">
         <v>4.0999999999999996</v>
       </c>
-      <c r="J20" s="10">
+      <c r="J20" s="9">
         <v>5.3811999999999998</v>
       </c>
-    </row>
-    <row r="21" spans="1:10">
+      <c r="K20" s="10">
+        <v>5.4984280700000001</v>
+      </c>
+      <c r="L20" s="12">
+        <v>5.4889862000000003</v>
+      </c>
+      <c r="M20" s="13">
+        <v>4.6099108299999996</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" t="s">
         <v>101</v>
       </c>
@@ -1845,7 +1979,7 @@
       <c r="F21" s="8">
         <v>29.103999999999999</v>
       </c>
-      <c r="G21" s="9">
+      <c r="G21" s="7">
         <v>4.3</v>
       </c>
       <c r="H21" s="2">
@@ -1854,11 +1988,20 @@
       <c r="I21" s="2">
         <v>3.1</v>
       </c>
-      <c r="J21" s="10">
+      <c r="J21" s="9">
         <v>4.7460000000000004</v>
       </c>
-    </row>
-    <row r="22" spans="1:10">
+      <c r="K21" s="10">
+        <v>5.5346868000000002</v>
+      </c>
+      <c r="L21" s="12">
+        <v>5.3406469300000001</v>
+      </c>
+      <c r="M21" s="13">
+        <v>4.6379685999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" t="s">
         <v>102</v>
       </c>
@@ -1877,7 +2020,7 @@
       <c r="F22" s="8">
         <v>27.431000000000001</v>
       </c>
-      <c r="G22" s="9">
+      <c r="G22" s="7">
         <v>4.2</v>
       </c>
       <c r="H22" s="2">
@@ -1886,11 +2029,20 @@
       <c r="I22" s="2">
         <v>3.4</v>
       </c>
-      <c r="J22" s="10">
+      <c r="J22" s="9">
         <v>4.4131</v>
       </c>
-    </row>
-    <row r="23" spans="1:10">
+      <c r="K22" s="10">
+        <v>5.0883249700000004</v>
+      </c>
+      <c r="L22" s="12">
+        <v>5.0674824699999999</v>
+      </c>
+      <c r="M22" s="13">
+        <v>4.3382035999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" t="s">
         <v>103</v>
       </c>
@@ -1909,7 +2061,7 @@
       <c r="F23" s="8">
         <v>27.05</v>
       </c>
-      <c r="G23" s="9">
+      <c r="G23" s="7">
         <v>3.6</v>
       </c>
       <c r="H23" s="2">
@@ -1918,11 +2070,20 @@
       <c r="I23" s="2">
         <v>3</v>
       </c>
-      <c r="J23" s="10">
+      <c r="J23" s="9">
         <v>3.9929999999999999</v>
       </c>
-    </row>
-    <row r="24" spans="1:10">
+      <c r="K23" s="10">
+        <v>5.1396746699999998</v>
+      </c>
+      <c r="L23" s="12">
+        <v>4.8421602000000004</v>
+      </c>
+      <c r="M23" s="13">
+        <v>4.3944953699999996</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24" t="s">
         <v>104</v>
       </c>
@@ -1941,7 +2102,7 @@
       <c r="F24" s="8">
         <v>27.856999999999999</v>
       </c>
-      <c r="G24" s="9">
+      <c r="G24" s="7">
         <v>3.6</v>
       </c>
       <c r="H24" s="2">
@@ -1950,11 +2111,20 @@
       <c r="I24" s="2">
         <v>3.3</v>
       </c>
-      <c r="J24" s="10">
+      <c r="J24" s="9">
         <v>4.3289999999999997</v>
       </c>
-    </row>
-    <row r="25" spans="1:10">
+      <c r="K24" s="10">
+        <v>4.8651426999999998</v>
+      </c>
+      <c r="L24" s="12">
+        <v>4.7308111300000002</v>
+      </c>
+      <c r="M24" s="13">
+        <v>4.2056846700000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
       <c r="A25" t="s">
         <v>105</v>
       </c>
@@ -1973,7 +2143,7 @@
       <c r="F25" s="8">
         <v>27.791</v>
       </c>
-      <c r="G25" s="9">
+      <c r="G25" s="7">
         <v>3.4</v>
       </c>
       <c r="H25" s="2">
@@ -1982,11 +2152,20 @@
       <c r="I25" s="2">
         <v>2.8</v>
       </c>
-      <c r="J25" s="10">
+      <c r="J25" s="9">
         <v>4.2131999999999996</v>
       </c>
-    </row>
-    <row r="26" spans="1:10">
+      <c r="K25" s="10">
+        <v>4.6338346000000001</v>
+      </c>
+      <c r="L25" s="12">
+        <v>4.4326927300000003</v>
+      </c>
+      <c r="M25" s="13">
+        <v>4.0575349699999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
       <c r="A26" t="s">
         <v>106</v>
       </c>
@@ -2005,7 +2184,7 @@
       <c r="F26" s="8">
         <v>29.193000000000001</v>
       </c>
-      <c r="G26" s="9">
+      <c r="G26" s="7">
         <v>3.5</v>
       </c>
       <c r="H26" s="2">
@@ -2014,11 +2193,20 @@
       <c r="I26" s="2">
         <v>3.3</v>
       </c>
-      <c r="J26" s="10">
+      <c r="J26" s="9">
         <v>3.9744000000000002</v>
       </c>
-    </row>
-    <row r="27" spans="1:10">
+      <c r="K26" s="10">
+        <v>4.4931961300000003</v>
+      </c>
+      <c r="L26" s="12">
+        <v>4.2295887299999997</v>
+      </c>
+      <c r="M26" s="13">
+        <v>3.96653893</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27" t="s">
         <v>107</v>
       </c>
@@ -2037,7 +2225,7 @@
       <c r="F27" s="8">
         <v>17.001999999999999</v>
       </c>
-      <c r="G27" s="9">
+      <c r="G27" s="7">
         <v>3.1</v>
       </c>
       <c r="H27" s="2">
@@ -2046,11 +2234,20 @@
       <c r="I27" s="2">
         <v>2.7</v>
       </c>
-      <c r="J27" s="10">
+      <c r="J27" s="9">
         <v>3.3332999999999999</v>
       </c>
-    </row>
-    <row r="28" spans="1:10">
+      <c r="K27" s="10">
+        <v>3.9979073700000001</v>
+      </c>
+      <c r="L27" s="12">
+        <v>3.8091588999999999</v>
+      </c>
+      <c r="M27" s="13">
+        <v>3.6378439</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28" t="s">
         <v>108</v>
       </c>
@@ -2069,7 +2266,7 @@
       <c r="F28" s="8">
         <v>13.92</v>
       </c>
-      <c r="G28" s="9">
+      <c r="G28" s="7">
         <v>1.7</v>
       </c>
       <c r="H28" s="2">
@@ -2078,11 +2275,20 @@
       <c r="I28" s="2">
         <v>2.7</v>
       </c>
-      <c r="J28" s="10">
+      <c r="J28" s="9">
         <v>3.1524000000000001</v>
       </c>
-    </row>
-    <row r="29" spans="1:10">
+      <c r="K28" s="10">
+        <v>3.69622647</v>
+      </c>
+      <c r="L28" s="12">
+        <v>3.11092163</v>
+      </c>
+      <c r="M28" s="13">
+        <v>3.4533513299999998</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29" t="s">
         <v>109</v>
       </c>
@@ -2101,7 +2307,7 @@
       <c r="F29" s="8">
         <v>13.86</v>
       </c>
-      <c r="G29" s="9">
+      <c r="G29" s="7">
         <v>1.7</v>
       </c>
       <c r="H29" s="2">
@@ -2110,11 +2316,20 @@
       <c r="I29" s="2">
         <v>2.9</v>
       </c>
-      <c r="J29" s="10">
+      <c r="J29" s="9">
         <v>2.6154999999999999</v>
       </c>
-    </row>
-    <row r="30" spans="1:10">
+      <c r="K29" s="10">
+        <v>3.5798593699999999</v>
+      </c>
+      <c r="L29" s="12">
+        <v>3.4550239999999999</v>
+      </c>
+      <c r="M29" s="13">
+        <v>3.3636947699999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
       <c r="A30" t="s">
         <v>110</v>
       </c>
@@ -2133,7 +2348,7 @@
       <c r="F30" s="8">
         <v>15.378</v>
       </c>
-      <c r="G30" s="9">
+      <c r="G30" s="7">
         <v>1.3</v>
       </c>
       <c r="H30" s="2">
@@ -2142,11 +2357,20 @@
       <c r="I30" s="2">
         <v>3</v>
       </c>
-      <c r="J30" s="10">
+      <c r="J30" s="9">
         <v>3.1114999999999999</v>
       </c>
-    </row>
-    <row r="31" spans="1:10">
+      <c r="K30" s="10">
+        <v>3.5567019700000002</v>
+      </c>
+      <c r="L30" s="12">
+        <v>3.4431558</v>
+      </c>
+      <c r="M30" s="13">
+        <v>3.3527504299999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" t="s">
         <v>111</v>
       </c>
@@ -2165,7 +2389,7 @@
       <c r="F31" s="8">
         <v>18.228999999999999</v>
       </c>
-      <c r="G31" s="9">
+      <c r="G31" s="7">
         <v>2</v>
       </c>
       <c r="H31" s="2">
@@ -2174,11 +2398,20 @@
       <c r="I31" s="2">
         <v>3</v>
       </c>
-      <c r="J31" s="10">
+      <c r="J31" s="9">
         <v>3.7037</v>
       </c>
-    </row>
-    <row r="32" spans="1:10">
+      <c r="K31" s="10">
+        <v>3.4771669699999999</v>
+      </c>
+      <c r="L31" s="12">
+        <v>3.3804077299999999</v>
+      </c>
+      <c r="M31" s="13">
+        <v>3.2985071000000001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
       <c r="A32" t="s">
         <v>112</v>
       </c>
@@ -2197,7 +2430,7 @@
       <c r="F32" s="8">
         <v>19.364000000000001</v>
       </c>
-      <c r="G32" s="9">
+      <c r="G32" s="7">
         <v>3.7</v>
       </c>
       <c r="H32" s="2">
@@ -2206,11 +2439,20 @@
       <c r="I32" s="2">
         <v>3.2</v>
       </c>
-      <c r="J32" s="10">
+      <c r="J32" s="9">
         <v>3.9182000000000001</v>
       </c>
-    </row>
-    <row r="33" spans="1:10">
+      <c r="K32" s="10">
+        <v>3.8370294999999999</v>
+      </c>
+      <c r="L32" s="12">
+        <v>3.8432135000000001</v>
+      </c>
+      <c r="M32" s="13">
+        <v>3.5334176300000002</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
       <c r="A33" t="s">
         <v>113</v>
       </c>
@@ -2229,7 +2471,7 @@
       <c r="F33" s="8">
         <v>20.385000000000002</v>
       </c>
-      <c r="G33" s="9">
+      <c r="G33" s="7">
         <v>4.2</v>
       </c>
       <c r="H33" s="2">
@@ -2238,11 +2480,20 @@
       <c r="I33" s="2">
         <v>3.1</v>
       </c>
-      <c r="J33" s="10">
+      <c r="J33" s="9">
         <v>4.1420000000000003</v>
       </c>
-    </row>
-    <row r="34" spans="1:10">
+      <c r="K33" s="10">
+        <v>4.0557199300000004</v>
+      </c>
+      <c r="L33" s="12">
+        <v>4.1366898000000001</v>
+      </c>
+      <c r="M33" s="13">
+        <v>3.6748677299999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
       <c r="A34" t="s">
         <v>114</v>
       </c>
@@ -2261,7 +2512,7 @@
       <c r="F34" s="8">
         <v>18.670000000000002</v>
       </c>
-      <c r="G34" s="9">
+      <c r="G34" s="7">
         <v>4.4000000000000004</v>
       </c>
       <c r="H34" s="2">
@@ -2270,11 +2521,20 @@
       <c r="I34" s="2">
         <v>3.2</v>
       </c>
-      <c r="J34" s="10">
+      <c r="J34" s="9">
         <v>3.6194999999999999</v>
       </c>
-    </row>
-    <row r="35" spans="1:10">
+      <c r="K34" s="10">
+        <v>4.2285899300000001</v>
+      </c>
+      <c r="L34" s="12">
+        <v>4.1464480000000004</v>
+      </c>
+      <c r="M34" s="13">
+        <v>3.7982592999999998</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
       <c r="A35" t="s">
         <v>115</v>
       </c>
@@ -2293,7 +2553,7 @@
       <c r="F35" s="8">
         <v>16.713999999999999</v>
       </c>
-      <c r="G35" s="9">
+      <c r="G35" s="7">
         <v>4</v>
       </c>
       <c r="H35" s="2">
@@ -2302,11 +2562,20 @@
       <c r="I35" s="2">
         <v>3.2</v>
       </c>
-      <c r="J35" s="10">
+      <c r="J35" s="9">
         <v>3.7610000000000001</v>
       </c>
-    </row>
-    <row r="36" spans="1:10">
+      <c r="K35" s="10">
+        <v>3.95956033</v>
+      </c>
+      <c r="L35" s="12">
+        <v>3.7101399000000002</v>
+      </c>
+      <c r="M35" s="13">
+        <v>3.62821433</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
       <c r="A36" t="s">
         <v>116</v>
       </c>
@@ -2325,7 +2594,7 @@
       <c r="F36" s="8">
         <v>17.280999999999999</v>
       </c>
-      <c r="G36" s="9">
+      <c r="G36" s="7">
         <v>4</v>
       </c>
       <c r="H36" s="2">
@@ -2334,11 +2603,20 @@
       <c r="I36" s="2">
         <v>3.4</v>
       </c>
-      <c r="J36" s="10">
+      <c r="J36" s="9">
         <v>3.9434999999999998</v>
       </c>
-    </row>
-    <row r="37" spans="1:10">
+      <c r="K36" s="10">
+        <v>4.0681033299999996</v>
+      </c>
+      <c r="L36" s="12">
+        <v>4.0097212000000004</v>
+      </c>
+      <c r="M36" s="13">
+        <v>3.6849010299999998</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13">
       <c r="A37" t="s">
         <v>117</v>
       </c>
@@ -2357,7 +2635,7 @@
       <c r="F37" s="8">
         <v>15.163</v>
       </c>
-      <c r="G37" s="9">
+      <c r="G37" s="7">
         <v>4.0999999999999996</v>
       </c>
       <c r="H37" s="2">
@@ -2366,11 +2644,20 @@
       <c r="I37" s="2">
         <v>4.3</v>
       </c>
-      <c r="J37" s="10">
+      <c r="J37" s="9">
         <v>4.1837999999999997</v>
       </c>
-    </row>
-    <row r="38" spans="1:10">
+      <c r="K37" s="10">
+        <v>4.1117827699999996</v>
+      </c>
+      <c r="L37" s="12">
+        <v>4.3490423700000003</v>
+      </c>
+      <c r="M37" s="13">
+        <v>3.6975690999999999</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13">
       <c r="A38" t="s">
         <v>118</v>
       </c>
@@ -2389,7 +2676,7 @@
       <c r="F38" s="8">
         <v>14.68</v>
       </c>
-      <c r="G38" s="9">
+      <c r="G38" s="7">
         <v>4.3</v>
       </c>
       <c r="H38" s="2">
@@ -2398,11 +2685,20 @@
       <c r="I38" s="2">
         <v>3.8</v>
       </c>
-      <c r="J38" s="10">
+      <c r="J38" s="9">
         <v>4.3689</v>
       </c>
-    </row>
-    <row r="39" spans="1:10">
+      <c r="K38" s="10">
+        <v>4.0578042700000001</v>
+      </c>
+      <c r="L38" s="12">
+        <v>4.3612560299999998</v>
+      </c>
+      <c r="M38" s="13">
+        <v>3.6578160999999998</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13">
       <c r="A39" t="s">
         <v>119</v>
       </c>
@@ -2421,7 +2717,7 @@
       <c r="F39" s="8">
         <v>18.417999999999999</v>
       </c>
-      <c r="G39" s="9">
+      <c r="G39" s="7">
         <v>4.7</v>
       </c>
       <c r="H39" s="2">
@@ -2430,11 +2726,20 @@
       <c r="I39" s="2">
         <v>3.8</v>
       </c>
-      <c r="J39" s="10">
+      <c r="J39" s="9">
         <v>4.5564</v>
       </c>
-    </row>
-    <row r="40" spans="1:10">
+      <c r="K39" s="10">
+        <v>4.2691099299999999</v>
+      </c>
+      <c r="L39" s="12">
+        <v>4.4704927000000003</v>
+      </c>
+      <c r="M39" s="13">
+        <v>3.8017903300000002</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13">
       <c r="A40" t="s">
         <v>120</v>
       </c>
@@ -2453,7 +2758,7 @@
       <c r="F40" s="8">
         <v>20.359000000000002</v>
       </c>
-      <c r="G40" s="9">
+      <c r="G40" s="7">
         <v>5.2</v>
       </c>
       <c r="H40" s="2">
@@ -2462,11 +2767,20 @@
       <c r="I40" s="2">
         <v>4.2</v>
       </c>
-      <c r="J40" s="10">
+      <c r="J40" s="9">
         <v>4.5777000000000001</v>
       </c>
-    </row>
-    <row r="41" spans="1:10">
+      <c r="K40" s="10">
+        <v>4.1085879299999997</v>
+      </c>
+      <c r="L40" s="12">
+        <v>4.64652083</v>
+      </c>
+      <c r="M40" s="13">
+        <v>3.67162107</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13">
       <c r="A41" t="s">
         <v>121</v>
       </c>
@@ -2485,7 +2799,7 @@
       <c r="F41" s="8">
         <v>19.253</v>
       </c>
-      <c r="G41" s="9">
+      <c r="G41" s="7">
         <v>4.7</v>
       </c>
       <c r="H41" s="2">
@@ -2494,11 +2808,20 @@
       <c r="I41" s="2">
         <v>3.7</v>
       </c>
-      <c r="J41" s="10">
+      <c r="J41" s="9">
         <v>4.3205</v>
       </c>
-    </row>
-    <row r="42" spans="1:10">
+      <c r="K41" s="10">
+        <v>3.7059770699999999</v>
+      </c>
+      <c r="L41" s="12">
+        <v>4.1584194700000001</v>
+      </c>
+      <c r="M41" s="13">
+        <v>3.4128206300000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13">
       <c r="A42" t="s">
         <v>122</v>
       </c>
@@ -2517,7 +2840,7 @@
       <c r="F42" s="8">
         <v>20.332999999999998</v>
       </c>
-      <c r="G42" s="9">
+      <c r="G42" s="7">
         <v>4.5999999999999996</v>
       </c>
       <c r="H42" s="2">
@@ -2526,11 +2849,20 @@
       <c r="I42" s="2">
         <v>3.5</v>
       </c>
-      <c r="J42" s="10">
+      <c r="J42" s="9">
         <v>3.9843999999999999</v>
       </c>
-    </row>
-    <row r="43" spans="1:10">
+      <c r="K42" s="10">
+        <v>3.7257347699999999</v>
+      </c>
+      <c r="L42" s="12">
+        <v>3.96104667</v>
+      </c>
+      <c r="M42" s="13">
+        <v>3.4372025700000002</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13">
       <c r="A43" t="s">
         <v>123</v>
       </c>
@@ -2549,7 +2881,7 @@
       <c r="F43" s="8">
         <v>21.722000000000001</v>
       </c>
-      <c r="G43" s="9">
+      <c r="G43" s="7">
         <v>5.2</v>
       </c>
       <c r="H43" s="2">
@@ -2558,11 +2890,20 @@
       <c r="I43" s="2">
         <v>4</v>
       </c>
-      <c r="J43" s="10">
+      <c r="J43" s="9">
         <v>4.0217000000000001</v>
       </c>
-    </row>
-    <row r="44" spans="1:10">
+      <c r="K43" s="10">
+        <v>3.9067440000000002</v>
+      </c>
+      <c r="L43" s="12">
+        <v>4.1920147300000004</v>
+      </c>
+      <c r="M43" s="13">
+        <v>3.5531233699999998</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13">
       <c r="A44" t="s">
         <v>124</v>
       </c>
@@ -2581,7 +2922,7 @@
       <c r="F44" s="8">
         <v>17.896999999999998</v>
       </c>
-      <c r="G44" s="9">
+      <c r="G44" s="7">
         <v>4.5999999999999996</v>
       </c>
       <c r="H44" s="2">
@@ -2590,11 +2931,20 @@
       <c r="I44" s="2">
         <v>3.6</v>
       </c>
-      <c r="J44" s="10">
+      <c r="J44" s="9">
         <v>3.8168000000000002</v>
       </c>
-    </row>
-    <row r="45" spans="1:10">
+      <c r="K44" s="10">
+        <v>4.0161228299999996</v>
+      </c>
+      <c r="L44" s="12">
+        <v>4.1907233699999997</v>
+      </c>
+      <c r="M44" s="13">
+        <v>3.6300307300000001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13">
       <c r="A45" t="s">
         <v>125</v>
       </c>
@@ -2613,7 +2963,7 @@
       <c r="F45" s="8">
         <v>26.5</v>
       </c>
-      <c r="G45" s="9">
+      <c r="G45" s="7">
         <v>5.6</v>
       </c>
       <c r="H45" s="2">
@@ -2622,11 +2972,20 @@
       <c r="I45" s="2">
         <v>4.2</v>
       </c>
-      <c r="J45" s="10">
+      <c r="J45" s="9">
         <v>4.3840000000000003</v>
       </c>
-    </row>
-    <row r="46" spans="1:10">
+      <c r="K45" s="10">
+        <v>3.9209755300000002</v>
+      </c>
+      <c r="L45" s="12">
+        <v>4.3101608300000001</v>
+      </c>
+      <c r="M45" s="13">
+        <v>3.55947513</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13">
       <c r="A46" t="s">
         <v>126</v>
       </c>
@@ -2645,7 +3004,7 @@
       <c r="F46" s="8">
         <v>31.853000000000002</v>
       </c>
-      <c r="G46" s="9">
+      <c r="G46" s="7">
         <v>6.3</v>
       </c>
       <c r="H46" s="2">
@@ -2654,11 +3013,20 @@
       <c r="I46" s="2">
         <v>4.7</v>
       </c>
-      <c r="J46" s="10">
+      <c r="J46" s="9">
         <v>4.2648999999999999</v>
       </c>
-    </row>
-    <row r="47" spans="1:10">
+      <c r="K46" s="10">
+        <v>3.9430409000000002</v>
+      </c>
+      <c r="L46" s="12">
+        <v>4.9504671299999998</v>
+      </c>
+      <c r="M46" s="13">
+        <v>3.5523693700000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13">
       <c r="A47" t="s">
         <v>127</v>
       </c>
@@ -2677,7 +3045,7 @@
       <c r="F47" s="8">
         <v>21.780999999999999</v>
       </c>
-      <c r="G47" s="9">
+      <c r="G47" s="7">
         <v>5.3</v>
       </c>
       <c r="H47" s="2">
@@ -2686,11 +3054,20 @@
       <c r="I47" s="2">
         <v>3.5</v>
       </c>
-      <c r="J47" s="10">
+      <c r="J47" s="9">
         <v>3.4944000000000002</v>
       </c>
-    </row>
-    <row r="48" spans="1:10">
+      <c r="K47" s="10">
+        <v>3.7995597299999999</v>
+      </c>
+      <c r="L47" s="12">
+        <v>3.8844827300000002</v>
+      </c>
+      <c r="M47" s="13">
+        <v>3.5028190700000001</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13">
       <c r="A48" t="s">
         <v>128</v>
       </c>
@@ -2709,7 +3086,7 @@
       <c r="F48" s="8">
         <v>20.753</v>
       </c>
-      <c r="G48" s="9">
+      <c r="G48" s="7">
         <v>4.8</v>
       </c>
       <c r="H48" s="2">
@@ -2718,11 +3095,20 @@
       <c r="I48" s="2">
         <v>3.2</v>
       </c>
-      <c r="J48" s="10">
+      <c r="J48" s="9">
         <v>3.3824000000000001</v>
       </c>
-    </row>
-    <row r="49" spans="1:10">
+      <c r="K48" s="10">
+        <v>3.8045613700000001</v>
+      </c>
+      <c r="L48" s="12">
+        <v>3.6586261699999998</v>
+      </c>
+      <c r="M48" s="13">
+        <v>3.51540337</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13">
       <c r="A49" t="s">
         <v>129</v>
       </c>
@@ -2741,7 +3127,7 @@
       <c r="F49" s="8">
         <v>21.655000000000001</v>
       </c>
-      <c r="G49" s="9">
+      <c r="G49" s="7">
         <v>3.9</v>
       </c>
       <c r="H49" s="2">
@@ -2750,11 +3136,20 @@
       <c r="I49" s="2">
         <v>3.1</v>
       </c>
-      <c r="J49" s="10">
+      <c r="J49" s="9">
         <v>3.3527999999999998</v>
       </c>
-    </row>
-    <row r="50" spans="1:10">
+      <c r="K49" s="10">
+        <v>3.81210973</v>
+      </c>
+      <c r="L49" s="12">
+        <v>3.7354417999999998</v>
+      </c>
+      <c r="M49" s="13">
+        <v>3.5186421700000001</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13">
       <c r="A50" t="s">
         <v>130</v>
       </c>
@@ -2773,7 +3168,7 @@
       <c r="F50" s="8">
         <v>21.736999999999998</v>
       </c>
-      <c r="G50" s="9">
+      <c r="G50" s="7">
         <v>3</v>
       </c>
       <c r="H50" s="2">
@@ -2782,11 +3177,20 @@
       <c r="I50" s="2">
         <v>2.9</v>
       </c>
-      <c r="J50" s="10">
+      <c r="J50" s="9">
         <v>3.1930000000000001</v>
       </c>
-    </row>
-    <row r="51" spans="1:10">
+      <c r="K50" s="10">
+        <v>3.5462250700000002</v>
+      </c>
+      <c r="L50" s="12">
+        <v>3.54553173</v>
+      </c>
+      <c r="M50" s="13">
+        <v>3.3445778000000002</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13">
       <c r="A51" t="s">
         <v>131</v>
       </c>
@@ -2805,7 +3209,7 @@
       <c r="F51" s="8">
         <v>18.91</v>
       </c>
-      <c r="G51" s="9">
+      <c r="G51" s="7">
         <v>2.9</v>
       </c>
       <c r="H51" s="2">
@@ -2814,11 +3218,20 @@
       <c r="I51" s="2">
         <v>2.6</v>
       </c>
-      <c r="J51" s="10">
+      <c r="J51" s="9">
         <v>3.2498</v>
       </c>
-    </row>
-    <row r="52" spans="1:10">
+      <c r="K51" s="10">
+        <v>3.5179933299999999</v>
+      </c>
+      <c r="L51" s="12">
+        <v>3.4001520300000001</v>
+      </c>
+      <c r="M51" s="13">
+        <v>3.3356611300000001</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13">
       <c r="A52" t="s">
         <v>132</v>
       </c>
@@ -2837,7 +3250,7 @@
       <c r="F52" s="8">
         <v>21.186</v>
       </c>
-      <c r="G52" s="9">
+      <c r="G52" s="7">
         <v>3.1</v>
       </c>
       <c r="H52" s="2">
@@ -2846,11 +3259,20 @@
       <c r="I52" s="2">
         <v>3</v>
       </c>
-      <c r="J52" s="10">
+      <c r="J52" s="9">
         <v>3.1074000000000002</v>
       </c>
-    </row>
-    <row r="53" spans="1:10">
+      <c r="K52" s="10">
+        <v>3.6332184000000001</v>
+      </c>
+      <c r="L52" s="12">
+        <v>3.4443123</v>
+      </c>
+      <c r="M52" s="13">
+        <v>3.4153857699999999</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13">
       <c r="A53" t="s">
         <v>133</v>
       </c>
@@ -2869,7 +3291,7 @@
       <c r="F53" s="8">
         <v>21.67</v>
       </c>
-      <c r="G53" s="9">
+      <c r="G53" s="7">
         <v>3.1</v>
       </c>
       <c r="H53" s="2">
@@ -2878,11 +3300,20 @@
       <c r="I53" s="2">
         <v>2.8</v>
       </c>
-      <c r="J53" s="10">
+      <c r="J53" s="9">
         <v>2.7909000000000002</v>
       </c>
-    </row>
-    <row r="54" spans="1:10">
+      <c r="K53" s="10">
+        <v>3.32348533</v>
+      </c>
+      <c r="L53" s="12">
+        <v>3.1331306699999999</v>
+      </c>
+      <c r="M53" s="13">
+        <v>3.2136250300000002</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13">
       <c r="A54" t="s">
         <v>134</v>
       </c>
@@ -2901,7 +3332,7 @@
       <c r="F54" s="8">
         <v>20.478999999999999</v>
       </c>
-      <c r="G54" s="9">
+      <c r="G54" s="7">
         <v>3.1</v>
       </c>
       <c r="H54" s="2">
@@ -2910,11 +3341,20 @@
       <c r="I54" s="2">
         <v>2.8</v>
       </c>
-      <c r="J54" s="10">
+      <c r="J54" s="9">
         <v>2.7065999999999999</v>
       </c>
-    </row>
-    <row r="55" spans="1:10">
+      <c r="K54" s="10">
+        <v>3.2896638999999999</v>
+      </c>
+      <c r="L54" s="12">
+        <v>3.0162698699999999</v>
+      </c>
+      <c r="M54" s="13">
+        <v>3.1964539300000001</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13">
       <c r="A55" t="s">
         <v>135</v>
       </c>
@@ -2933,7 +3373,7 @@
       <c r="F55" s="8">
         <v>19.824999999999999</v>
       </c>
-      <c r="G55" s="9">
+      <c r="G55" s="7">
         <v>3.2</v>
       </c>
       <c r="H55" s="2">
@@ -2942,11 +3382,20 @@
       <c r="I55" s="2">
         <v>3.1</v>
       </c>
-      <c r="J55" s="10">
+      <c r="J55" s="9">
         <v>2.7801999999999998</v>
       </c>
-    </row>
-    <row r="56" spans="1:10">
+      <c r="K55" s="10">
+        <v>3.1762714000000001</v>
+      </c>
+      <c r="L55" s="12">
+        <v>2.9790464000000001</v>
+      </c>
+      <c r="M55" s="13">
+        <v>3.11831587</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13">
       <c r="A56" t="s">
         <v>136</v>
       </c>
@@ -2965,7 +3414,7 @@
       <c r="F56" s="8">
         <v>19.760000000000002</v>
       </c>
-      <c r="G56" s="9">
+      <c r="G56" s="7">
         <v>3.1</v>
       </c>
       <c r="H56" s="2">
@@ -2974,11 +3423,20 @@
       <c r="I56" s="2">
         <v>3.1</v>
       </c>
-      <c r="J56" s="10">
+      <c r="J56" s="9">
         <v>2.7557999999999998</v>
       </c>
-    </row>
-    <row r="57" spans="1:10">
+      <c r="K56" s="10">
+        <v>3.0223519300000001</v>
+      </c>
+      <c r="L56" s="12">
+        <v>2.84716893</v>
+      </c>
+      <c r="M56" s="13">
+        <v>3.0151429699999999</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13">
       <c r="A57" t="s">
         <v>137</v>
       </c>
@@ -2997,7 +3455,7 @@
       <c r="F57" s="8">
         <v>17.795999999999999</v>
       </c>
-      <c r="G57" s="9">
+      <c r="G57" s="7">
         <v>2.8</v>
       </c>
       <c r="H57" s="2">
@@ -3006,11 +3464,20 @@
       <c r="I57" s="2">
         <v>3.1</v>
       </c>
-      <c r="J57" s="10">
+      <c r="J57" s="9">
         <v>3.0522</v>
       </c>
-    </row>
-    <row r="58" spans="1:10">
+      <c r="K57" s="10">
+        <v>2.9288990699999999</v>
+      </c>
+      <c r="L57" s="12">
+        <v>2.77914167</v>
+      </c>
+      <c r="M57" s="13">
+        <v>2.95220467</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13">
       <c r="A58" t="s">
         <v>138</v>
       </c>
@@ -3029,7 +3496,7 @@
       <c r="F58" s="8">
         <v>16.451000000000001</v>
       </c>
-      <c r="G58" s="9">
+      <c r="G58" s="7">
         <v>2.8</v>
       </c>
       <c r="H58" s="2">
@@ -3038,11 +3505,20 @@
       <c r="I58" s="2">
         <v>3</v>
       </c>
-      <c r="J58" s="10">
+      <c r="J58" s="9">
         <v>2.8332000000000002</v>
       </c>
-    </row>
-    <row r="59" spans="1:10">
+      <c r="K58" s="10">
+        <v>2.9141195999999998</v>
+      </c>
+      <c r="L58" s="12">
+        <v>2.7457907700000002</v>
+      </c>
+      <c r="M58" s="13">
+        <v>2.9438580999999999</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13">
       <c r="A59" t="s">
         <v>139</v>
       </c>
@@ -3061,7 +3537,7 @@
       <c r="F59" s="8">
         <v>14.813000000000001</v>
       </c>
-      <c r="G59" s="9">
+      <c r="G59" s="7">
         <v>2.5</v>
       </c>
       <c r="H59" s="2">
@@ -3070,11 +3546,20 @@
       <c r="I59" s="2">
         <v>2.9</v>
       </c>
-      <c r="J59" s="10">
+      <c r="J59" s="9">
         <v>2.7631000000000001</v>
       </c>
-    </row>
-    <row r="60" spans="1:10">
+      <c r="K59" s="10">
+        <v>3.0634859699999999</v>
+      </c>
+      <c r="L59" s="12">
+        <v>2.9771223</v>
+      </c>
+      <c r="M59" s="13">
+        <v>3.03912643</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13">
       <c r="A60" t="s">
         <v>140</v>
       </c>
@@ -3093,7 +3578,7 @@
       <c r="F60" s="8">
         <v>17.777000000000001</v>
       </c>
-      <c r="G60" s="9">
+      <c r="G60" s="7">
         <v>2.4</v>
       </c>
       <c r="H60" s="2">
@@ -3102,11 +3587,20 @@
       <c r="I60" s="2">
         <v>2.9</v>
       </c>
-      <c r="J60" s="10">
+      <c r="J60" s="9">
         <v>2.8923999999999999</v>
       </c>
-    </row>
-    <row r="61" spans="1:10">
+      <c r="K60" s="10">
+        <v>3.4732972700000002</v>
+      </c>
+      <c r="L60" s="12">
+        <v>3.2953144999999999</v>
+      </c>
+      <c r="M60" s="13">
+        <v>3.30897993</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13">
       <c r="A61" t="s">
         <v>141</v>
       </c>
@@ -3125,7 +3619,7 @@
       <c r="F61" s="8">
         <v>18.497</v>
       </c>
-      <c r="G61" s="9">
+      <c r="G61" s="7">
         <v>2.9</v>
       </c>
       <c r="H61" s="2">
@@ -3134,11 +3628,20 @@
       <c r="I61" s="2">
         <v>3.1</v>
       </c>
-      <c r="J61" s="10">
+      <c r="J61" s="9">
         <v>3.0516999999999999</v>
       </c>
-    </row>
-    <row r="62" spans="1:10">
+      <c r="K61" s="10">
+        <v>3.5102900300000002</v>
+      </c>
+      <c r="L61" s="12">
+        <v>3.2748912300000002</v>
+      </c>
+      <c r="M61" s="13">
+        <v>3.33382383</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13">
       <c r="A62" t="s">
         <v>142</v>
       </c>
@@ -3157,7 +3660,7 @@
       <c r="F62" s="8">
         <v>17.657</v>
       </c>
-      <c r="G62" s="9">
+      <c r="G62" s="7">
         <v>2.6</v>
       </c>
       <c r="H62" s="2">
@@ -3166,11 +3669,20 @@
       <c r="I62" s="2">
         <v>3.1</v>
       </c>
-      <c r="J62" s="10">
+      <c r="J62" s="9">
         <v>3.1029</v>
       </c>
-    </row>
-    <row r="63" spans="1:10">
+      <c r="K62" s="10">
+        <v>3.7548176999999998</v>
+      </c>
+      <c r="L62" s="12">
+        <v>3.6598178699999999</v>
+      </c>
+      <c r="M62" s="13">
+        <v>3.4860519999999999</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13">
       <c r="A63" t="s">
         <v>143</v>
       </c>
@@ -3189,7 +3701,7 @@
       <c r="F63" s="8">
         <v>18.356999999999999</v>
       </c>
-      <c r="G63" s="9">
+      <c r="G63" s="7">
         <v>2.8</v>
       </c>
       <c r="H63" s="2">
@@ -3198,11 +3710,20 @@
       <c r="I63" s="2">
         <v>3.1</v>
       </c>
-      <c r="J63" s="10">
+      <c r="J63" s="9">
         <v>2.8929</v>
       </c>
-    </row>
-    <row r="64" spans="1:10">
+      <c r="K63" s="10">
+        <v>3.7372576</v>
+      </c>
+      <c r="L63" s="12">
+        <v>3.57933747</v>
+      </c>
+      <c r="M63" s="13">
+        <v>3.4765161</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13">
       <c r="A64" t="s">
         <v>144</v>
       </c>
@@ -3221,7 +3742,7 @@
       <c r="F64" s="8">
         <v>19.343</v>
       </c>
-      <c r="G64" s="9">
+      <c r="G64" s="7">
         <v>3.1</v>
       </c>
       <c r="H64" s="2">
@@ -3230,11 +3751,20 @@
       <c r="I64" s="2">
         <v>3.1</v>
       </c>
-      <c r="J64" s="10">
+      <c r="J64" s="9">
         <v>2.9361999999999999</v>
       </c>
-    </row>
-    <row r="65" spans="1:10">
+      <c r="K64" s="10">
+        <v>3.2893111300000002</v>
+      </c>
+      <c r="L64" s="12">
+        <v>3.3292601999999998</v>
+      </c>
+      <c r="M64" s="13">
+        <v>3.1673347700000001</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13">
       <c r="A65" t="s">
         <v>145</v>
       </c>
@@ -3253,7 +3783,7 @@
       <c r="F65" s="8">
         <v>17.853000000000002</v>
       </c>
-      <c r="G65" s="9">
+      <c r="G65" s="7">
         <v>2.7</v>
       </c>
       <c r="H65" s="2">
@@ -3262,11 +3792,20 @@
       <c r="I65" s="2">
         <v>2.9</v>
       </c>
-      <c r="J65" s="10">
+      <c r="J65" s="9">
         <v>2.5676999999999999</v>
       </c>
-    </row>
-    <row r="66" spans="1:10">
+      <c r="K65" s="10">
+        <v>3.12339967</v>
+      </c>
+      <c r="L65" s="12">
+        <v>3.2447513300000002</v>
+      </c>
+      <c r="M65" s="13">
+        <v>3.0566861300000001</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13">
       <c r="A66" t="s">
         <v>146</v>
       </c>
@@ -3285,7 +3824,7 @@
       <c r="F66" s="8">
         <v>18.157</v>
       </c>
-      <c r="G66" s="9">
+      <c r="G66" s="7">
         <v>2.6</v>
       </c>
       <c r="H66" s="2">
@@ -3294,11 +3833,20 @@
       <c r="I66" s="2">
         <v>2.8</v>
       </c>
-      <c r="J66" s="10">
+      <c r="J66" s="9">
         <v>2.3504999999999998</v>
       </c>
-    </row>
-    <row r="67" spans="1:10">
+      <c r="K66" s="10">
+        <v>2.9762854000000001</v>
+      </c>
+      <c r="L66" s="12">
+        <v>2.95539167</v>
+      </c>
+      <c r="M66" s="13">
+        <v>2.9642043999999999</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13">
       <c r="A67" t="s">
         <v>147</v>
       </c>
@@ -3317,7 +3865,7 @@
       <c r="F67" s="8">
         <v>19.77</v>
       </c>
-      <c r="G67" s="9">
+      <c r="G67" s="7">
         <v>2.8</v>
       </c>
       <c r="H67" s="2">
@@ -3326,11 +3874,20 @@
       <c r="I67" s="2">
         <v>2.8</v>
       </c>
-      <c r="J67" s="10">
+      <c r="J67" s="9">
         <v>2.3622999999999998</v>
       </c>
-    </row>
-    <row r="68" spans="1:10">
+      <c r="K67" s="10">
+        <v>2.9038630699999999</v>
+      </c>
+      <c r="L67" s="12">
+        <v>2.8467725000000002</v>
+      </c>
+      <c r="M67" s="13">
+        <v>2.9195450300000001</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13">
       <c r="A68" t="s">
         <v>148</v>
       </c>
@@ -3349,7 +3906,7 @@
       <c r="F68" s="8">
         <v>21.757000000000001</v>
       </c>
-      <c r="G68" s="9">
+      <c r="G68" s="7">
         <v>2.8</v>
       </c>
       <c r="H68" s="2">
@@ -3358,11 +3915,20 @@
       <c r="I68" s="2">
         <v>3</v>
       </c>
-      <c r="J68" s="10">
+      <c r="J68" s="9">
         <v>2.5023</v>
       </c>
-    </row>
-    <row r="69" spans="1:10">
+      <c r="K68" s="10">
+        <v>3.24879367</v>
+      </c>
+      <c r="L68" s="12">
+        <v>3.20243973</v>
+      </c>
+      <c r="M68" s="13">
+        <v>3.1472137999999998</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13">
       <c r="A69" t="s">
         <v>149</v>
       </c>
@@ -3381,7 +3947,7 @@
       <c r="F69" s="8">
         <v>22.422999999999998</v>
       </c>
-      <c r="G69" s="9">
+      <c r="G69" s="7">
         <v>2.9</v>
       </c>
       <c r="H69" s="2">
@@ -3390,11 +3956,20 @@
       <c r="I69" s="2">
         <v>3.1</v>
       </c>
-      <c r="J69" s="10">
+      <c r="J69" s="9">
         <v>2.5049999999999999</v>
       </c>
-    </row>
-    <row r="70" spans="1:10">
+      <c r="K69" s="10">
+        <v>3.2915960700000002</v>
+      </c>
+      <c r="L69" s="12">
+        <v>3.1289913</v>
+      </c>
+      <c r="M69" s="13">
+        <v>3.1797472299999998</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13">
       <c r="A70" t="s">
         <v>150</v>
       </c>
@@ -3413,7 +3988,7 @@
       <c r="F70" s="8">
         <v>24.667000000000002</v>
       </c>
-      <c r="G70" s="9">
+      <c r="G70" s="7">
         <v>3.2</v>
       </c>
       <c r="H70" s="2">
@@ -3422,11 +3997,20 @@
       <c r="I70" s="2">
         <v>3</v>
       </c>
-      <c r="J70" s="10">
+      <c r="J70" s="9">
         <v>2.5649999999999999</v>
       </c>
-    </row>
-    <row r="71" spans="1:10">
+      <c r="K70" s="10">
+        <v>3.16999377</v>
+      </c>
+      <c r="L70" s="12">
+        <v>3.080832</v>
+      </c>
+      <c r="M70" s="13">
+        <v>3.09766823</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13">
       <c r="A71" t="s">
         <v>151</v>
       </c>
@@ -3445,7 +4029,7 @@
       <c r="F71" s="8">
         <v>22.79</v>
       </c>
-      <c r="G71" s="9">
+      <c r="G71" s="7">
         <v>2.9</v>
       </c>
       <c r="H71" s="2">
@@ -3454,11 +4038,20 @@
       <c r="I71" s="2">
         <v>2.9</v>
       </c>
-      <c r="J71" s="10">
+      <c r="J71" s="9">
         <v>2.5781999999999998</v>
       </c>
-    </row>
-    <row r="72" spans="1:10">
+      <c r="K71" s="10">
+        <v>3.2455742700000001</v>
+      </c>
+      <c r="L71" s="12">
+        <v>3.1742476700000002</v>
+      </c>
+      <c r="M71" s="13">
+        <v>3.1480256999999998</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13">
       <c r="A72" t="s">
         <v>152</v>
       </c>
@@ -3477,7 +4070,7 @@
       <c r="F72" s="8">
         <v>19.907</v>
       </c>
-      <c r="G72" s="9">
+      <c r="G72" s="7">
         <v>2.2999999999999998</v>
       </c>
       <c r="H72" s="2">
@@ -3486,11 +4079,20 @@
       <c r="I72" s="2">
         <v>2.9</v>
       </c>
-      <c r="J72" s="10">
+      <c r="J72" s="9">
         <v>2.423</v>
       </c>
-    </row>
-    <row r="73" spans="1:10">
+      <c r="K72" s="10">
+        <v>3.3250242700000001</v>
+      </c>
+      <c r="L72" s="12">
+        <v>3.1893510699999998</v>
+      </c>
+      <c r="M72" s="13">
+        <v>3.2016266299999998</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13">
       <c r="A73" t="s">
         <v>153</v>
       </c>
@@ -3509,7 +4111,7 @@
       <c r="F73" s="8">
         <v>19.783000000000001</v>
       </c>
-      <c r="G73" s="9">
+      <c r="G73" s="7">
         <v>2.2000000000000002</v>
       </c>
       <c r="H73" s="2">
@@ -3518,11 +4120,20 @@
       <c r="I73" s="2">
         <v>2.7</v>
       </c>
-      <c r="J73" s="10">
+      <c r="J73" s="9">
         <v>2.4550000000000001</v>
       </c>
-    </row>
-    <row r="74" spans="1:10">
+      <c r="K73" s="10">
+        <v>3.15833933</v>
+      </c>
+      <c r="L73" s="12">
+        <v>3.0243427999999999</v>
+      </c>
+      <c r="M73" s="13">
+        <v>3.0905008299999999</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13">
       <c r="A74" t="s">
         <v>154</v>
       </c>
@@ -3541,7 +4152,7 @@
       <c r="F74" s="8">
         <v>19.917000000000002</v>
       </c>
-      <c r="G74" s="9">
+      <c r="G74" s="7">
         <v>1.9</v>
       </c>
       <c r="H74" s="2">
@@ -3550,11 +4161,20 @@
       <c r="I74" s="2">
         <v>2.8</v>
       </c>
-      <c r="J74" s="10">
+      <c r="J74" s="9">
         <v>2.2968000000000002</v>
       </c>
-    </row>
-    <row r="75" spans="1:10">
+      <c r="K74" s="10">
+        <v>3.0661783699999998</v>
+      </c>
+      <c r="L74" s="12">
+        <v>2.9521174299999999</v>
+      </c>
+      <c r="M74" s="13">
+        <v>3.0304473999999999</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13">
       <c r="A75" t="s">
         <v>155</v>
       </c>
@@ -3573,7 +4193,7 @@
       <c r="F75" s="8">
         <v>15.93</v>
       </c>
-      <c r="G75" s="9">
+      <c r="G75" s="7">
         <v>1.5</v>
       </c>
       <c r="H75" s="2">
@@ -3582,11 +4202,20 @@
       <c r="I75" s="2">
         <v>2.4</v>
       </c>
-      <c r="J75" s="10">
+      <c r="J75" s="9">
         <v>2.2338</v>
       </c>
-    </row>
-    <row r="76" spans="1:10">
+      <c r="K75" s="10">
+        <v>2.936839</v>
+      </c>
+      <c r="L75" s="12">
+        <v>2.7487349299999999</v>
+      </c>
+      <c r="M75" s="13">
+        <v>2.9467585299999999</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13">
       <c r="A76" t="s">
         <v>156</v>
       </c>
@@ -3605,7 +4234,7 @@
       <c r="F76" s="8">
         <v>14.653</v>
       </c>
-      <c r="G76" s="9">
+      <c r="G76" s="7">
         <v>1.6</v>
       </c>
       <c r="H76" s="2">
@@ -3614,11 +4243,20 @@
       <c r="I76" s="2">
         <v>2.6</v>
       </c>
-      <c r="J76" s="10">
+      <c r="J76" s="9">
         <v>2.0482999999999998</v>
       </c>
-    </row>
-    <row r="77" spans="1:10">
+      <c r="K76" s="10">
+        <v>2.9390829300000001</v>
+      </c>
+      <c r="L76" s="12">
+        <v>2.6122002000000002</v>
+      </c>
+      <c r="M76" s="13">
+        <v>2.9547254299999999</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13">
       <c r="A77" t="s">
         <v>157</v>
       </c>
@@ -3637,7 +4275,7 @@
       <c r="F77" s="8">
         <v>14.13</v>
       </c>
-      <c r="G77" s="9">
+      <c r="G77" s="7">
         <v>1.6</v>
       </c>
       <c r="H77" s="2">
@@ -3646,11 +4284,20 @@
       <c r="I77" s="2">
         <v>2.4</v>
       </c>
-      <c r="J77" s="10">
+      <c r="J77" s="9">
         <v>2.0345</v>
       </c>
-    </row>
-    <row r="78" spans="1:10">
+      <c r="K77" s="10">
+        <v>2.86074933</v>
+      </c>
+      <c r="L77" s="12">
+        <v>2.6607547299999998</v>
+      </c>
+      <c r="M77" s="13">
+        <v>2.89891817</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13">
       <c r="A78" t="s">
         <v>158</v>
       </c>
@@ -3669,7 +4316,7 @@
       <c r="F78" s="8">
         <v>12.84</v>
       </c>
-      <c r="G78" s="9">
+      <c r="G78" s="7">
         <v>1.5</v>
       </c>
       <c r="H78" s="2">
@@ -3678,11 +4325,20 @@
       <c r="I78" s="2">
         <v>2.4</v>
       </c>
-      <c r="J78" s="10">
+      <c r="J78" s="9">
         <v>1.8525</v>
       </c>
-    </row>
-    <row r="79" spans="1:10">
+      <c r="K78" s="10">
+        <v>2.4843892300000001</v>
+      </c>
+      <c r="L78" s="12">
+        <v>2.32549173</v>
+      </c>
+      <c r="M78" s="13">
+        <v>2.6517032999999999</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13">
       <c r="A79" t="s">
         <v>159</v>
       </c>
@@ -3701,7 +4357,7 @@
       <c r="F79" s="8">
         <v>13.047000000000001</v>
       </c>
-      <c r="G79" s="9">
+      <c r="G79" s="7">
         <v>1.7</v>
       </c>
       <c r="H79" s="2">
@@ -3710,11 +4366,20 @@
       <c r="I79" s="2">
         <v>2.6</v>
       </c>
-      <c r="J79" s="10">
+      <c r="J79" s="9">
         <v>1.5446</v>
       </c>
-    </row>
-    <row r="80" spans="1:10">
+      <c r="K79" s="10">
+        <v>2.6671925999999999</v>
+      </c>
+      <c r="L79" s="12">
+        <v>2.5083721300000001</v>
+      </c>
+      <c r="M79" s="13">
+        <v>2.7711160000000001</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13">
       <c r="A80" t="s">
         <v>160</v>
       </c>
@@ -3733,7 +4398,7 @@
       <c r="F80" s="8">
         <v>17.66</v>
       </c>
-      <c r="G80" s="9">
+      <c r="G80" s="7">
         <v>2.1</v>
       </c>
       <c r="H80" s="2">
@@ -3742,11 +4407,20 @@
       <c r="I80" s="2">
         <v>2.7</v>
       </c>
-      <c r="J80" s="10">
+      <c r="J80" s="9">
         <v>1.7404999999999999</v>
       </c>
-    </row>
-    <row r="81" spans="1:10">
+      <c r="K80" s="10">
+        <v>2.8608256700000001</v>
+      </c>
+      <c r="L80" s="12">
+        <v>2.59680423</v>
+      </c>
+      <c r="M80" s="13">
+        <v>2.8992953699999999</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13">
       <c r="A81" t="s">
         <v>161</v>
       </c>
@@ -3765,7 +4439,7 @@
       <c r="F81" s="8">
         <v>21.736999999999998</v>
       </c>
-      <c r="G81" s="9">
+      <c r="G81" s="7">
         <v>2.2999999999999998</v>
       </c>
       <c r="H81" s="2">
@@ -3774,11 +4448,20 @@
       <c r="I81" s="2">
         <v>2.7</v>
       </c>
-      <c r="J81" s="10">
+      <c r="J81" s="9">
         <v>1.8674999999999999</v>
       </c>
-    </row>
-    <row r="82" spans="1:10">
+      <c r="K81" s="10">
+        <v>3.0533912999999999</v>
+      </c>
+      <c r="L81" s="12">
+        <v>2.7673423000000001</v>
+      </c>
+      <c r="M81" s="13">
+        <v>3.0288243000000001</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13">
       <c r="A82" t="s">
         <v>162</v>
       </c>
@@ -3797,7 +4480,7 @@
       <c r="F82" s="8">
         <v>24.562999999999999</v>
       </c>
-      <c r="G82" s="9">
+      <c r="G82" s="7">
         <v>2.6</v>
       </c>
       <c r="H82" s="2">
@@ -3806,11 +4489,20 @@
       <c r="I82" s="2">
         <v>2.9</v>
       </c>
-      <c r="J82" s="10">
+      <c r="J82" s="9">
         <v>1.8129999999999999</v>
       </c>
-    </row>
-    <row r="83" spans="1:10">
+      <c r="K82" s="10">
+        <v>3.1671529</v>
+      </c>
+      <c r="L82" s="12">
+        <v>3.0087436699999999</v>
+      </c>
+      <c r="M82" s="13">
+        <v>3.1007720299999999</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13">
       <c r="A83" t="s">
         <v>163</v>
       </c>
@@ -3829,7 +4521,7 @@
       <c r="F83" s="8">
         <v>28.806999999999999</v>
       </c>
-      <c r="G83" s="9">
+      <c r="G83" s="7">
         <v>3.3</v>
       </c>
       <c r="H83" s="2">
@@ -3838,11 +4530,20 @@
       <c r="I83" s="2">
         <v>3</v>
       </c>
-      <c r="J83" s="10">
+      <c r="J83" s="9">
         <v>1.9881</v>
       </c>
-    </row>
-    <row r="84" spans="1:10">
+      <c r="K83" s="10">
+        <v>3.3172853299999998</v>
+      </c>
+      <c r="L83" s="12">
+        <v>3.1587374700000002</v>
+      </c>
+      <c r="M83" s="13">
+        <v>3.1957451300000002</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13">
       <c r="A84" t="s">
         <v>164</v>
       </c>
@@ -3861,7 +4562,7 @@
       <c r="F84" s="8">
         <v>28.783000000000001</v>
       </c>
-      <c r="G84" s="9">
+      <c r="G84" s="7">
         <v>3.3</v>
       </c>
       <c r="H84" s="2">
@@ -3870,11 +4571,20 @@
       <c r="I84" s="2">
         <v>3</v>
       </c>
-      <c r="J84" s="10">
+      <c r="J84" s="9">
         <v>2.2149999999999999</v>
       </c>
-    </row>
-    <row r="85" spans="1:10">
+      <c r="K84" s="10">
+        <v>3.2589822000000002</v>
+      </c>
+      <c r="L84" s="12">
+        <v>3.41116683</v>
+      </c>
+      <c r="M84" s="13">
+        <v>3.1442102699999999</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13">
       <c r="A85" t="s">
         <v>165</v>
       </c>
@@ -3893,7 +4603,7 @@
       <c r="F85" s="8">
         <v>31.623000000000001</v>
       </c>
-      <c r="G85" s="9">
+      <c r="G85" s="7">
         <v>3.5</v>
       </c>
       <c r="H85" s="2">
@@ -3902,11 +4612,20 @@
       <c r="I85" s="2">
         <v>2.9</v>
       </c>
-      <c r="J85" s="10">
+      <c r="J85" s="9">
         <v>2.3742999999999999</v>
       </c>
-    </row>
-    <row r="86" spans="1:10">
+      <c r="K85" s="10">
+        <v>3.0476560699999999</v>
+      </c>
+      <c r="L85" s="12">
+        <v>3.1279634700000001</v>
+      </c>
+      <c r="M85" s="13">
+        <v>3.0034479300000001</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13">
       <c r="A86" t="s">
         <v>166</v>
       </c>
@@ -3925,7 +4644,7 @@
       <c r="F86" s="8">
         <v>31.98</v>
       </c>
-      <c r="G86" s="9">
+      <c r="G86" s="7">
         <v>3.4</v>
       </c>
       <c r="H86" s="2">
@@ -3934,11 +4653,20 @@
       <c r="I86" s="2">
         <v>3</v>
       </c>
-      <c r="J86" s="10">
+      <c r="J86" s="9">
         <v>2.2595000000000001</v>
       </c>
-    </row>
-    <row r="87" spans="1:10">
+      <c r="K86" s="10">
+        <v>2.9310508300000002</v>
+      </c>
+      <c r="L86" s="12">
+        <v>3.1241631000000001</v>
+      </c>
+      <c r="M86" s="13">
+        <v>2.9221881299999999</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13">
       <c r="A87" t="s">
         <v>167</v>
       </c>
@@ -3957,7 +4685,7 @@
       <c r="F87" s="8">
         <v>28.81</v>
       </c>
-      <c r="G87" s="9">
+      <c r="G87" s="7">
         <v>3.4</v>
       </c>
       <c r="H87" s="2">
@@ -3966,11 +4694,20 @@
       <c r="I87" s="2">
         <v>2.9</v>
       </c>
-      <c r="J87" s="10">
+      <c r="J87" s="9">
         <v>2.1217999999999999</v>
       </c>
-    </row>
-    <row r="88" spans="1:10">
+      <c r="K87" s="10">
+        <v>2.55793223</v>
+      </c>
+      <c r="L87" s="12">
+        <v>2.4760114</v>
+      </c>
+      <c r="M87" s="13">
+        <v>2.6897744299999999</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13">
       <c r="A88" t="s">
         <v>168</v>
       </c>
@@ -3989,7 +4726,7 @@
       <c r="F88" s="8">
         <v>27.882999999999999</v>
       </c>
-      <c r="G88" s="9">
+      <c r="G88" s="7">
         <v>3.3</v>
       </c>
       <c r="H88" s="2">
@@ -3998,11 +4735,20 @@
       <c r="I88" s="2">
         <v>3.1</v>
       </c>
-      <c r="J88" s="10">
+      <c r="J88" s="9">
         <v>2.0695999999999999</v>
       </c>
-    </row>
-    <row r="89" spans="1:10">
+      <c r="K88" s="10">
+        <v>2.73134283</v>
+      </c>
+      <c r="L88" s="12">
+        <v>2.6780914999999998</v>
+      </c>
+      <c r="M88" s="13">
+        <v>2.8110851299999999</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13">
       <c r="A89" t="s">
         <v>169</v>
       </c>
@@ -4021,7 +4767,7 @@
       <c r="F89" s="8">
         <v>26.6</v>
       </c>
-      <c r="G89" s="9">
+      <c r="G89" s="7">
         <v>2.7</v>
       </c>
       <c r="H89" s="2">
@@ -4030,11 +4776,20 @@
       <c r="I89" s="2">
         <v>2.7</v>
       </c>
-      <c r="J89" s="10">
+      <c r="J89" s="9">
         <v>2.0891000000000002</v>
       </c>
-    </row>
-    <row r="90" spans="1:10">
+      <c r="K89" s="10">
+        <v>2.7474823000000002</v>
+      </c>
+      <c r="L89" s="12">
+        <v>2.7963411699999998</v>
+      </c>
+      <c r="M89" s="13">
+        <v>2.8190292700000001</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13">
       <c r="A90" t="s">
         <v>170</v>
       </c>
@@ -4053,7 +4808,7 @@
       <c r="F90" s="8">
         <v>20.402999999999999</v>
       </c>
-      <c r="G90" s="9">
+      <c r="G90" s="7">
         <v>1.9</v>
       </c>
       <c r="H90" s="2">
@@ -4062,11 +4817,20 @@
       <c r="I90" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="J90" s="10">
+      <c r="J90" s="9">
         <v>1.7377</v>
       </c>
-    </row>
-    <row r="91" spans="1:10">
+      <c r="K90" s="10">
+        <v>2.5212699700000001</v>
+      </c>
+      <c r="L90" s="12">
+        <v>2.36800203</v>
+      </c>
+      <c r="M90" s="13">
+        <v>2.6836619000000002</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13">
       <c r="A91" t="s">
         <v>171</v>
       </c>
@@ -4085,7 +4849,7 @@
       <c r="F91" s="8">
         <v>21.61</v>
       </c>
-      <c r="G91" s="9">
+      <c r="G91" s="7">
         <v>1.2</v>
       </c>
       <c r="H91" s="2">
@@ -4094,11 +4858,20 @@
       <c r="I91" s="2">
         <v>2.2000000000000002</v>
       </c>
-      <c r="J91" s="10">
+      <c r="J91" s="9">
         <v>1.7831999999999999</v>
       </c>
-    </row>
-    <row r="92" spans="1:10">
+      <c r="K91" s="10">
+        <v>2.7356563</v>
+      </c>
+      <c r="L91" s="12">
+        <v>2.14997353</v>
+      </c>
+      <c r="M91" s="13">
+        <v>2.8460581</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13">
       <c r="A92" t="s">
         <v>172</v>
       </c>
@@ -4117,7 +4890,7 @@
       <c r="F92" s="8">
         <v>26.27</v>
       </c>
-      <c r="G92" s="9">
+      <c r="G92" s="7">
         <v>1.3</v>
       </c>
       <c r="H92" s="2">
@@ -4126,11 +4899,20 @@
       <c r="I92" s="2">
         <v>2.7</v>
       </c>
-      <c r="J92" s="10">
+      <c r="J92" s="9">
         <v>1.9280999999999999</v>
       </c>
-    </row>
-    <row r="93" spans="1:10">
+      <c r="K92" s="10">
+        <v>2.8250630000000001</v>
+      </c>
+      <c r="L92" s="12">
+        <v>2.51613687</v>
+      </c>
+      <c r="M92" s="13">
+        <v>2.8946456299999999</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13">
       <c r="A93" t="s">
         <v>173</v>
       </c>
@@ -4149,7 +4931,7 @@
       <c r="F93" s="8">
         <v>28.33</v>
       </c>
-      <c r="G93" s="9">
+      <c r="G93" s="7">
         <v>1.6</v>
       </c>
       <c r="H93" s="2">
@@ -4158,11 +4940,20 @@
       <c r="I93" s="2">
         <v>2.6</v>
       </c>
-      <c r="J93" s="10">
+      <c r="J93" s="9">
         <v>1.8935999999999999</v>
       </c>
-    </row>
-    <row r="94" spans="1:10">
+      <c r="K93" s="10">
+        <v>2.4191783999999998</v>
+      </c>
+      <c r="L93" s="12">
+        <v>2.1735607699999999</v>
+      </c>
+      <c r="M93" s="13">
+        <v>2.6250108700000001</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13">
       <c r="A94" t="s">
         <v>174</v>
       </c>
@@ -4181,7 +4972,7 @@
       <c r="F94" s="8">
         <v>28.18</v>
       </c>
-      <c r="G94" s="9">
+      <c r="G94" s="7">
         <v>2.2999999999999998</v>
       </c>
       <c r="H94" s="2">
@@ -4190,11 +4981,20 @@
       <c r="I94" s="2">
         <v>2.5</v>
       </c>
-      <c r="J94" s="10">
+      <c r="J94" s="9">
         <v>1.9253</v>
       </c>
-    </row>
-    <row r="95" spans="1:10">
+      <c r="K94" s="10">
+        <v>2.2136469999999999</v>
+      </c>
+      <c r="L94" s="12">
+        <v>1.9956967999999999</v>
+      </c>
+      <c r="M94" s="13">
+        <v>2.4901788300000001</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13">
       <c r="A95" t="s">
         <v>175</v>
       </c>
@@ -4213,7 +5013,7 @@
       <c r="F95" s="8">
         <v>34.119999999999997</v>
       </c>
-      <c r="G95" s="9">
+      <c r="G95" s="7">
         <v>3</v>
       </c>
       <c r="H95" s="2">
@@ -4222,11 +5022,20 @@
       <c r="I95" s="2">
         <v>2.8</v>
       </c>
-      <c r="J95" s="10">
+      <c r="J95" s="9">
         <v>1.8409</v>
       </c>
-    </row>
-    <row r="96" spans="1:10">
+      <c r="K95" s="10">
+        <v>2.1892966299999999</v>
+      </c>
+      <c r="L95" s="12">
+        <v>2.0296309699999999</v>
+      </c>
+      <c r="M95" s="13">
+        <v>2.4708412700000002</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13">
       <c r="A96" t="s">
         <v>176</v>
       </c>
@@ -4245,7 +5054,7 @@
       <c r="F96" s="8">
         <v>29.036999999999999</v>
       </c>
-      <c r="G96" s="9">
+      <c r="G96" s="7">
         <v>2</v>
       </c>
       <c r="H96" s="2">
@@ -4254,11 +5063,20 @@
       <c r="I96" s="2">
         <v>2.2000000000000002</v>
       </c>
-      <c r="J96" s="10">
+      <c r="J96" s="9">
         <v>1.7747999999999999</v>
       </c>
-    </row>
-    <row r="97" spans="1:10">
+      <c r="K96" s="10">
+        <v>2.0708606700000001</v>
+      </c>
+      <c r="L96" s="12">
+        <v>2.0375917000000001</v>
+      </c>
+      <c r="M96" s="13">
+        <v>2.3869647999999999</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13">
       <c r="A97" t="s">
         <v>177</v>
       </c>
@@ -4277,7 +5095,7 @@
       <c r="F97" s="8">
         <v>30.213000000000001</v>
       </c>
-      <c r="G97" s="9">
+      <c r="G97" s="7">
         <v>2.2000000000000002</v>
       </c>
       <c r="H97" s="2">
@@ -4286,11 +5104,20 @@
       <c r="I97" s="2">
         <v>2.2999999999999998</v>
       </c>
-      <c r="J97" s="10">
+      <c r="J97" s="9">
         <v>1.7225999999999999</v>
       </c>
-    </row>
-    <row r="98" spans="1:10">
+      <c r="K97" s="10">
+        <v>2.2198460999999998</v>
+      </c>
+      <c r="L97" s="12">
+        <v>1.8198124</v>
+      </c>
+      <c r="M97" s="13">
+        <v>2.5021177300000002</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13">
       <c r="A98" t="s">
         <v>178</v>
       </c>
@@ -4309,7 +5136,7 @@
       <c r="F98" s="8">
         <v>31.19</v>
       </c>
-      <c r="G98" s="9">
+      <c r="G98" s="7">
         <v>2</v>
       </c>
       <c r="H98" s="2">
@@ -4318,11 +5145,20 @@
       <c r="I98" s="2">
         <v>2.6</v>
       </c>
-      <c r="J98" s="10">
+      <c r="J98" s="9">
         <v>1.7551000000000001</v>
       </c>
-    </row>
-    <row r="99" spans="1:10">
+      <c r="K98" s="10">
+        <v>2.2542806999999998</v>
+      </c>
+      <c r="L98" s="12">
+        <v>1.98093893</v>
+      </c>
+      <c r="M98" s="13">
+        <v>2.5206050699999998</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13">
       <c r="A99" t="s">
         <v>179</v>
       </c>
@@ -4341,7 +5177,7 @@
       <c r="F99" s="8">
         <v>35.256999999999998</v>
       </c>
-      <c r="G99" s="9">
+      <c r="G99" s="7">
         <v>1.8</v>
       </c>
       <c r="H99" s="2">
@@ -4350,11 +5186,20 @@
       <c r="I99" s="2">
         <v>2.7</v>
       </c>
-      <c r="J99" s="10">
+      <c r="J99" s="9">
         <v>1.5686</v>
       </c>
-    </row>
-    <row r="100" spans="1:10">
+      <c r="K99" s="10">
+        <v>2.2546310300000001</v>
+      </c>
+      <c r="L99" s="12">
+        <v>1.8661497</v>
+      </c>
+      <c r="M99" s="13">
+        <v>2.5260538299999999</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13">
       <c r="A100" t="s">
         <v>180</v>
       </c>
@@ -4373,7 +5218,7 @@
       <c r="F100" s="8">
         <v>38.33</v>
       </c>
-      <c r="G100" s="9">
+      <c r="G100" s="7">
         <v>2.8</v>
       </c>
       <c r="H100" s="2">
@@ -4382,11 +5227,20 @@
       <c r="I100" s="2">
         <v>3.3</v>
       </c>
-      <c r="J100" s="10">
+      <c r="J100" s="9">
         <v>1.8331</v>
       </c>
-    </row>
-    <row r="101" spans="1:10">
+      <c r="K100" s="10">
+        <v>2.3900448000000001</v>
+      </c>
+      <c r="L100" s="12">
+        <v>2.2136491</v>
+      </c>
+      <c r="M100" s="13">
+        <v>2.6074257699999999</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13">
       <c r="A101" t="s">
         <v>181</v>
       </c>
@@ -4405,7 +5259,7 @@
       <c r="F101" s="8">
         <v>43.86</v>
       </c>
-      <c r="G101" s="9">
+      <c r="G101" s="7">
         <v>2.7</v>
       </c>
       <c r="H101" s="2">
@@ -4414,11 +5268,20 @@
       <c r="I101" s="2">
         <v>2.9</v>
       </c>
-      <c r="J101" s="10">
+      <c r="J101" s="9">
         <v>2.1528</v>
       </c>
-    </row>
-    <row r="102" spans="1:10">
+      <c r="K101" s="10">
+        <v>2.4431248000000001</v>
+      </c>
+      <c r="L101" s="12">
+        <v>2.4244902000000002</v>
+      </c>
+      <c r="M101" s="13">
+        <v>2.6346635699999998</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13">
       <c r="A102" t="s">
         <v>182</v>
       </c>
@@ -4437,7 +5300,7 @@
       <c r="F102" s="8">
         <v>48.307000000000002</v>
       </c>
-      <c r="G102" s="9">
+      <c r="G102" s="7">
         <v>3.4</v>
       </c>
       <c r="H102" s="2">
@@ -4446,11 +5309,20 @@
       <c r="I102" s="2">
         <v>3</v>
       </c>
-      <c r="J102" s="10">
+      <c r="J102" s="9">
         <v>1.9992000000000001</v>
       </c>
-    </row>
-    <row r="103" spans="1:10">
+      <c r="K102" s="10">
+        <v>2.3348616299999998</v>
+      </c>
+      <c r="L102" s="12">
+        <v>2.0350611700000001</v>
+      </c>
+      <c r="M102" s="13">
+        <v>2.5703239999999998</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13">
       <c r="A103" t="s">
         <v>183</v>
       </c>
@@ -4469,7 +5341,7 @@
       <c r="F103" s="8">
         <v>49.707000000000001</v>
       </c>
-      <c r="G103" s="9">
+      <c r="G103" s="7">
         <v>3</v>
       </c>
       <c r="H103" s="2">
@@ -4478,11 +5350,20 @@
       <c r="I103" s="2">
         <v>3</v>
       </c>
-      <c r="J103" s="10">
+      <c r="J103" s="9">
         <v>1.9775</v>
       </c>
-    </row>
-    <row r="104" spans="1:10">
+      <c r="K103" s="10">
+        <v>2.4047695</v>
+      </c>
+      <c r="L103" s="12">
+        <v>2.20394823</v>
+      </c>
+      <c r="M103" s="13">
+        <v>2.61051067</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13">
       <c r="A104" t="s">
         <v>184</v>
       </c>
@@ -4501,7 +5382,7 @@
       <c r="F104" s="8">
         <v>53.042999999999999</v>
       </c>
-      <c r="G104" s="9">
+      <c r="G104" s="7">
         <v>2.9</v>
       </c>
       <c r="H104" s="2">
@@ -4510,11 +5391,20 @@
       <c r="I104" s="2">
         <v>3.2</v>
       </c>
-      <c r="J104" s="10">
+      <c r="J104" s="9">
         <v>2.2313000000000001</v>
       </c>
-    </row>
-    <row r="105" spans="1:10">
+      <c r="K104" s="10">
+        <v>2.4067037299999998</v>
+      </c>
+      <c r="L104" s="12">
+        <v>2.4674190299999998</v>
+      </c>
+      <c r="M104" s="13">
+        <v>2.5983849299999999</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13">
       <c r="A105" t="s">
         <v>185</v>
       </c>
@@ -4533,7 +5423,7 @@
       <c r="F105" s="8">
         <v>63.08</v>
       </c>
-      <c r="G105" s="9">
+      <c r="G105" s="7">
         <v>3.8</v>
       </c>
       <c r="H105" s="2">
@@ -4542,11 +5432,20 @@
       <c r="I105" s="2">
         <v>3.5</v>
       </c>
-      <c r="J105" s="10">
+      <c r="J105" s="9">
         <v>2.2452000000000001</v>
       </c>
-    </row>
-    <row r="106" spans="1:10">
+      <c r="K105" s="10">
+        <v>2.39480877</v>
+      </c>
+      <c r="L105" s="12">
+        <v>2.3831456700000002</v>
+      </c>
+      <c r="M105" s="13">
+        <v>2.58700347</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13">
       <c r="A106" t="s">
         <v>186</v>
       </c>
@@ -4565,7 +5464,7 @@
       <c r="F106" s="8">
         <v>60.033000000000001</v>
       </c>
-      <c r="G106" s="9">
+      <c r="G106" s="7">
         <v>3.7</v>
       </c>
       <c r="H106" s="2">
@@ -4574,11 +5473,20 @@
       <c r="I106" s="2">
         <v>3.7</v>
       </c>
-      <c r="J106" s="10">
+      <c r="J106" s="9">
         <v>2.1876000000000002</v>
       </c>
-    </row>
-    <row r="107" spans="1:10">
+      <c r="K106" s="10">
+        <v>2.5651291000000001</v>
+      </c>
+      <c r="L106" s="12">
+        <v>3.0418845700000001</v>
+      </c>
+      <c r="M106" s="13">
+        <v>2.67660053</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13">
       <c r="A107" t="s">
         <v>187</v>
       </c>
@@ -4597,7 +5505,7 @@
       <c r="F107" s="8">
         <v>63.347000000000001</v>
       </c>
-      <c r="G107" s="9">
+      <c r="G107" s="7">
         <v>3.7</v>
       </c>
       <c r="H107" s="2">
@@ -4606,11 +5514,20 @@
       <c r="I107" s="2">
         <v>3</v>
       </c>
-      <c r="J107" s="10">
+      <c r="J107" s="9">
         <v>2.1911</v>
       </c>
-    </row>
-    <row r="108" spans="1:10">
+      <c r="K107" s="10">
+        <v>2.4788540999999999</v>
+      </c>
+      <c r="L107" s="12">
+        <v>2.2265568299999998</v>
+      </c>
+      <c r="M107" s="13">
+        <v>2.6468346700000001</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13">
       <c r="A108" t="s">
         <v>188</v>
       </c>
@@ -4629,7 +5546,7 @@
       <c r="F108" s="8">
         <v>70.53</v>
       </c>
-      <c r="G108" s="9">
+      <c r="G108" s="7">
         <v>3.9</v>
       </c>
       <c r="H108" s="2">
@@ -4638,11 +5555,20 @@
       <c r="I108" s="2">
         <v>3.5</v>
       </c>
-      <c r="J108" s="10">
+      <c r="J108" s="9">
         <v>2.2606000000000002</v>
       </c>
-    </row>
-    <row r="109" spans="1:10">
+      <c r="K108" s="10">
+        <v>2.6517205000000001</v>
+      </c>
+      <c r="L108" s="12">
+        <v>2.7702709699999999</v>
+      </c>
+      <c r="M108" s="13">
+        <v>2.7461268699999999</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13">
       <c r="A109" t="s">
         <v>189</v>
       </c>
@@ -4661,7 +5587,7 @@
       <c r="F109" s="8">
         <v>70.442999999999998</v>
       </c>
-      <c r="G109" s="9">
+      <c r="G109" s="7">
         <v>3.3</v>
       </c>
       <c r="H109" s="2">
@@ -4670,11 +5596,20 @@
       <c r="I109" s="2">
         <v>3.4</v>
       </c>
-      <c r="J109" s="10">
+      <c r="J109" s="9">
         <v>2.3919000000000001</v>
       </c>
-    </row>
-    <row r="110" spans="1:10">
+      <c r="K109" s="10">
+        <v>2.61960237</v>
+      </c>
+      <c r="L109" s="12">
+        <v>2.7729631000000001</v>
+      </c>
+      <c r="M109" s="13">
+        <v>2.72169683</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13">
       <c r="A110" t="s">
         <v>190</v>
       </c>
@@ -4693,7 +5628,7 @@
       <c r="F110" s="8">
         <v>60.093000000000004</v>
       </c>
-      <c r="G110" s="9">
+      <c r="G110" s="7">
         <v>2</v>
       </c>
       <c r="H110" s="2">
@@ -4702,11 +5637,20 @@
       <c r="I110" s="2">
         <v>3</v>
       </c>
-      <c r="J110" s="10">
+      <c r="J110" s="9">
         <v>2.2698</v>
       </c>
-    </row>
-    <row r="111" spans="1:10">
+      <c r="K110" s="10">
+        <v>2.4038425700000001</v>
+      </c>
+      <c r="L110" s="12">
+        <v>2.0930832700000002</v>
+      </c>
+      <c r="M110" s="13">
+        <v>2.5944510699999999</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13">
       <c r="A111" t="s">
         <v>191</v>
       </c>
@@ -4725,7 +5669,7 @@
       <c r="F111" s="8">
         <v>58.13</v>
       </c>
-      <c r="G111" s="9">
+      <c r="G111" s="7">
         <v>2.4</v>
       </c>
       <c r="H111" s="2">
@@ -4734,11 +5678,20 @@
       <c r="I111" s="2">
         <v>3</v>
       </c>
-      <c r="J111" s="10">
+      <c r="J111" s="9">
         <v>2.1312000000000002</v>
       </c>
-    </row>
-    <row r="112" spans="1:10">
+      <c r="K111" s="10">
+        <v>2.5214612299999999</v>
+      </c>
+      <c r="L111" s="12">
+        <v>2.7070377699999999</v>
+      </c>
+      <c r="M111" s="13">
+        <v>2.6554839299999999</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13">
       <c r="A112" t="s">
         <v>192</v>
       </c>
@@ -4757,7 +5710,7 @@
       <c r="F112" s="8">
         <v>64.97</v>
       </c>
-      <c r="G112" s="9">
+      <c r="G112" s="7">
         <v>2.7</v>
       </c>
       <c r="H112" s="2">
@@ -4766,11 +5719,20 @@
       <c r="I112" s="2">
         <v>3.3</v>
       </c>
-      <c r="J112" s="10">
+      <c r="J112" s="9">
         <v>2.2921999999999998</v>
       </c>
-    </row>
-    <row r="113" spans="1:10">
+      <c r="K112" s="10">
+        <v>2.5583009300000001</v>
+      </c>
+      <c r="L112" s="12">
+        <v>2.9524565699999998</v>
+      </c>
+      <c r="M112" s="13">
+        <v>2.67404793</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13">
       <c r="A113" t="s">
         <v>193</v>
       </c>
@@ -4789,7 +5751,7 @@
       <c r="F113" s="8">
         <v>75.5</v>
       </c>
-      <c r="G113" s="9">
+      <c r="G113" s="7">
         <v>2.2999999999999998</v>
       </c>
       <c r="H113" s="2">
@@ -4798,11 +5760,20 @@
       <c r="I113" s="2">
         <v>3.2</v>
       </c>
-      <c r="J113" s="10">
+      <c r="J113" s="9">
         <v>2.2673000000000001</v>
       </c>
-    </row>
-    <row r="114" spans="1:10">
+      <c r="K113" s="10">
+        <v>2.51375613</v>
+      </c>
+      <c r="L113" s="12">
+        <v>2.6139644</v>
+      </c>
+      <c r="M113" s="13">
+        <v>2.6570567700000001</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13">
       <c r="A114" t="s">
         <v>194</v>
       </c>
@@ -4821,7 +5792,7 @@
       <c r="F114" s="8">
         <v>90.85</v>
       </c>
-      <c r="G114" s="9">
+      <c r="G114" s="7">
         <v>4</v>
       </c>
       <c r="H114" s="2">
@@ -4830,11 +5801,20 @@
       <c r="I114" s="2">
         <v>3.3</v>
       </c>
-      <c r="J114" s="10">
+      <c r="J114" s="9">
         <v>2.2425000000000002</v>
       </c>
-    </row>
-    <row r="115" spans="1:10">
+      <c r="K114" s="10">
+        <v>2.3277174299999999</v>
+      </c>
+      <c r="L114" s="12">
+        <v>2.4892767</v>
+      </c>
+      <c r="M114" s="13">
+        <v>2.5329338699999999</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13">
       <c r="A115" t="s">
         <v>195</v>
       </c>
@@ -4853,7 +5833,7 @@
       <c r="F115" s="8">
         <v>97.953000000000003</v>
       </c>
-      <c r="G115" s="9">
+      <c r="G115" s="7">
         <v>4.0999999999999996</v>
       </c>
       <c r="H115" s="2">
@@ -4862,11 +5842,20 @@
       <c r="I115" s="2">
         <v>3.8</v>
       </c>
-      <c r="J115" s="10">
+      <c r="J115" s="9">
         <v>2.2444999999999999</v>
       </c>
-    </row>
-    <row r="116" spans="1:10">
+      <c r="K115" s="10">
+        <v>2.0628457</v>
+      </c>
+      <c r="L115" s="12">
+        <v>2.2326950700000001</v>
+      </c>
+      <c r="M115" s="13">
+        <v>2.3663102999999999</v>
+      </c>
+    </row>
+    <row r="116" spans="1:13">
       <c r="A116" t="s">
         <v>196</v>
       </c>
@@ -4885,7 +5874,7 @@
       <c r="F116" s="8">
         <v>123.96299999999999</v>
       </c>
-      <c r="G116" s="9">
+      <c r="G116" s="7">
         <v>4.3</v>
       </c>
       <c r="H116" s="2">
@@ -4894,11 +5883,20 @@
       <c r="I116" s="2">
         <v>5</v>
       </c>
-      <c r="J116" s="10">
+      <c r="J116" s="9">
         <v>2.3917000000000002</v>
       </c>
-    </row>
-    <row r="117" spans="1:10">
+      <c r="K116" s="10">
+        <v>2.1749101999999998</v>
+      </c>
+      <c r="L116" s="12">
+        <v>2.3442864299999999</v>
+      </c>
+      <c r="M116" s="13">
+        <v>2.4457770000000001</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13">
       <c r="A117" t="s">
         <v>197</v>
       </c>
@@ -4917,7 +5915,7 @@
       <c r="F117" s="8">
         <v>117.983</v>
       </c>
-      <c r="G117" s="9">
+      <c r="G117" s="7">
         <v>5.3</v>
       </c>
       <c r="H117" s="2">
@@ -4926,11 +5924,20 @@
       <c r="I117" s="2">
         <v>4.7</v>
       </c>
-      <c r="J117" s="10">
+      <c r="J117" s="9">
         <v>2.2277</v>
       </c>
-    </row>
-    <row r="118" spans="1:10">
+      <c r="K117" s="10">
+        <v>2.2999659700000001</v>
+      </c>
+      <c r="L117" s="12">
+        <v>2.9108299299999998</v>
+      </c>
+      <c r="M117" s="13">
+        <v>2.51032323</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13">
       <c r="A118" t="s">
         <v>198</v>
       </c>
@@ -4949,7 +5956,7 @@
       <c r="F118" s="8">
         <v>58.37</v>
       </c>
-      <c r="G118" s="9">
+      <c r="G118" s="7">
         <v>1.6</v>
       </c>
       <c r="H118" s="2">
@@ -4958,11 +5965,20 @@
       <c r="I118" s="2">
         <v>2.8</v>
       </c>
-      <c r="J118" s="10">
+      <c r="J118" s="9">
         <v>1.9411</v>
       </c>
-    </row>
-    <row r="119" spans="1:10">
+      <c r="K118" s="10">
+        <v>1.89819647</v>
+      </c>
+      <c r="L118" s="12">
+        <v>0.89160238000000003</v>
+      </c>
+      <c r="M118" s="13">
+        <v>2.3056881699999998</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13">
       <c r="A119" t="s">
         <v>199</v>
       </c>
@@ -4981,7 +5997,7 @@
       <c r="F119" s="8">
         <v>42.96</v>
       </c>
-      <c r="G119" s="9">
+      <c r="G119" s="7">
         <v>-0.2</v>
       </c>
       <c r="H119" s="2">
@@ -4990,11 +6006,20 @@
       <c r="I119" s="2">
         <v>2</v>
       </c>
-      <c r="J119" s="10">
+      <c r="J119" s="9">
         <v>1.2529999999999999</v>
       </c>
-    </row>
-    <row r="120" spans="1:10">
+      <c r="K119" s="10">
+        <v>1.6413906700000001</v>
+      </c>
+      <c r="L119" s="12">
+        <v>0.12484797</v>
+      </c>
+      <c r="M119" s="13">
+        <v>2.1597169300000001</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13">
       <c r="A120" t="s">
         <v>200</v>
       </c>
@@ -5013,7 +6038,7 @@
       <c r="F120" s="8">
         <v>59.542999999999999</v>
       </c>
-      <c r="G120" s="9">
+      <c r="G120" s="7">
         <v>-0.9</v>
       </c>
       <c r="H120" s="2">
@@ -5022,11 +6047,20 @@
       <c r="I120" s="2">
         <v>2.9</v>
       </c>
-      <c r="J120" s="10">
+      <c r="J120" s="9">
         <v>1.4694</v>
       </c>
-    </row>
-    <row r="121" spans="1:10">
+      <c r="K120" s="10">
+        <v>1.85356217</v>
+      </c>
+      <c r="L120" s="12">
+        <v>1.2668979300000001</v>
+      </c>
+      <c r="M120" s="13">
+        <v>2.26804417</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13">
       <c r="A121" t="s">
         <v>201</v>
       </c>
@@ -5045,7 +6079,7 @@
       <c r="F121" s="8">
         <v>68.203000000000003</v>
       </c>
-      <c r="G121" s="9">
+      <c r="G121" s="7">
         <v>-1.6</v>
       </c>
       <c r="H121" s="2">
@@ -5054,11 +6088,20 @@
       <c r="I121" s="2">
         <v>2.6</v>
       </c>
-      <c r="J121" s="10">
+      <c r="J121" s="9">
         <v>1.4576</v>
       </c>
-    </row>
-    <row r="122" spans="1:10">
+      <c r="K121" s="10">
+        <v>2.0681110999999999</v>
+      </c>
+      <c r="L121" s="12">
+        <v>1.9791924999999999</v>
+      </c>
+      <c r="M121" s="13">
+        <v>2.3928236699999998</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13">
       <c r="A122" t="s">
         <v>202</v>
       </c>
@@ -5077,7 +6120,7 @@
       <c r="F122" s="8">
         <v>76.066999999999993</v>
       </c>
-      <c r="G122" s="9">
+      <c r="G122" s="7">
         <v>1.5</v>
       </c>
       <c r="H122" s="2">
@@ -5086,11 +6129,20 @@
       <c r="I122" s="2">
         <v>2.7</v>
       </c>
-      <c r="J122" s="10">
+      <c r="J122" s="9">
         <v>1.4816</v>
       </c>
-    </row>
-    <row r="123" spans="1:10">
+      <c r="K122" s="10">
+        <v>1.9619755299999999</v>
+      </c>
+      <c r="L122" s="12">
+        <v>1.7406668999999999</v>
+      </c>
+      <c r="M122" s="13">
+        <v>2.3297319299999999</v>
+      </c>
+    </row>
+    <row r="123" spans="1:13">
       <c r="A123" t="s">
         <v>203</v>
       </c>
@@ -5109,7 +6161,7 @@
       <c r="F123" s="8">
         <v>78.626999999999995</v>
       </c>
-      <c r="G123" s="9">
+      <c r="G123" s="7">
         <v>2.4</v>
       </c>
       <c r="H123" s="2">
@@ -5118,11 +6170,20 @@
       <c r="I123" s="2">
         <v>2.7</v>
       </c>
-      <c r="J123" s="10">
+      <c r="J123" s="9">
         <v>1.5317000000000001</v>
       </c>
-    </row>
-    <row r="124" spans="1:10">
+      <c r="K123" s="10">
+        <v>2.0381484300000001</v>
+      </c>
+      <c r="L123" s="12">
+        <v>1.7991717300000001</v>
+      </c>
+      <c r="M123" s="13">
+        <v>2.3817994300000001</v>
+      </c>
+    </row>
+    <row r="124" spans="1:13">
       <c r="A124" t="s">
         <v>204</v>
       </c>
@@ -5141,7 +6202,7 @@
       <c r="F124" s="8">
         <v>77.89</v>
       </c>
-      <c r="G124" s="9">
+      <c r="G124" s="7">
         <v>1.8</v>
       </c>
       <c r="H124" s="2">
@@ -5150,11 +6211,20 @@
       <c r="I124" s="2">
         <v>3</v>
       </c>
-      <c r="J124" s="10">
+      <c r="J124" s="9">
         <v>1.6557999999999999</v>
       </c>
-    </row>
-    <row r="125" spans="1:10">
+      <c r="K124" s="10">
+        <v>1.9892216300000001</v>
+      </c>
+      <c r="L124" s="12">
+        <v>1.5011276</v>
+      </c>
+      <c r="M124" s="13">
+        <v>2.3574272999999999</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13">
       <c r="A125" t="s">
         <v>205</v>
       </c>
@@ -5173,7 +6243,7 @@
       <c r="F125" s="8">
         <v>76.167000000000002</v>
       </c>
-      <c r="G125" s="9">
+      <c r="G125" s="7">
         <v>1.2</v>
       </c>
       <c r="H125" s="2">
@@ -5182,11 +6252,20 @@
       <c r="I125" s="2">
         <v>2.5</v>
       </c>
-      <c r="J125" s="10">
+      <c r="J125" s="9">
         <v>1.5025999999999999</v>
       </c>
-    </row>
-    <row r="126" spans="1:10">
+      <c r="K125" s="10">
+        <v>1.67330467</v>
+      </c>
+      <c r="L125" s="12">
+        <v>1.07035188</v>
+      </c>
+      <c r="M125" s="13">
+        <v>2.1528811700000001</v>
+      </c>
+    </row>
+    <row r="126" spans="1:13">
       <c r="A126" t="s">
         <v>206</v>
       </c>
@@ -5205,7 +6284,7 @@
       <c r="F126" s="8">
         <v>85.027000000000001</v>
       </c>
-      <c r="G126" s="9">
+      <c r="G126" s="7">
         <v>1.2</v>
       </c>
       <c r="H126" s="2">
@@ -5214,11 +6293,20 @@
       <c r="I126" s="2">
         <v>2.9</v>
       </c>
-      <c r="J126" s="10">
+      <c r="J126" s="9">
         <v>1.522</v>
       </c>
-    </row>
-    <row r="127" spans="1:10">
+      <c r="K126" s="10">
+        <v>1.60493993</v>
+      </c>
+      <c r="L126" s="12">
+        <v>1.4184570299999999</v>
+      </c>
+      <c r="M126" s="13">
+        <v>2.0919426300000001</v>
+      </c>
+    </row>
+    <row r="127" spans="1:13">
       <c r="A127" t="s">
         <v>207</v>
       </c>
@@ -5237,7 +6325,7 @@
       <c r="F127" s="8">
         <v>93.98</v>
       </c>
-      <c r="G127" s="9">
+      <c r="G127" s="7">
         <v>2.1</v>
       </c>
       <c r="H127" s="2">
@@ -5246,11 +6334,20 @@
       <c r="I127" s="2">
         <v>3.8</v>
       </c>
-      <c r="J127" s="10">
+      <c r="J127" s="9">
         <v>1.5032000000000001</v>
       </c>
-    </row>
-    <row r="128" spans="1:10">
+      <c r="K127" s="10">
+        <v>2.0018306300000002</v>
+      </c>
+      <c r="L127" s="12">
+        <v>1.9503892</v>
+      </c>
+      <c r="M127" s="13">
+        <v>2.2758362700000001</v>
+      </c>
+    </row>
+    <row r="128" spans="1:13">
       <c r="A128" t="s">
         <v>208</v>
       </c>
@@ -5269,7 +6366,7 @@
       <c r="F128" s="8">
         <v>102.553</v>
       </c>
-      <c r="G128" s="9">
+      <c r="G128" s="7">
         <v>3.3</v>
       </c>
       <c r="H128" s="2">
@@ -5278,11 +6375,20 @@
       <c r="I128" s="2">
         <v>4.2</v>
       </c>
-      <c r="J128" s="10">
+      <c r="J128" s="9">
         <v>1.7729999999999999</v>
       </c>
-    </row>
-    <row r="129" spans="1:10">
+      <c r="K128" s="10">
+        <v>2.0085433300000002</v>
+      </c>
+      <c r="L128" s="12">
+        <v>2.16191457</v>
+      </c>
+      <c r="M128" s="13">
+        <v>2.2737177700000002</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13">
       <c r="A129" t="s">
         <v>209</v>
       </c>
@@ -5301,7 +6407,7 @@
       <c r="F129" s="8">
         <v>89.71</v>
       </c>
-      <c r="G129" s="9">
+      <c r="G129" s="7">
         <v>3.7</v>
       </c>
       <c r="H129" s="2">
@@ -5310,11 +6416,20 @@
       <c r="I129" s="2">
         <v>3.4</v>
       </c>
-      <c r="J129" s="10">
+      <c r="J129" s="9">
         <v>1.8874</v>
       </c>
-    </row>
-    <row r="130" spans="1:10">
+      <c r="K129" s="10">
+        <v>1.75954937</v>
+      </c>
+      <c r="L129" s="12">
+        <v>1.6508462699999999</v>
+      </c>
+      <c r="M129" s="13">
+        <v>2.12771263</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13">
       <c r="A130" t="s">
         <v>210</v>
       </c>
@@ -5333,7 +6448,7 @@
       <c r="F130" s="8">
         <v>94.063000000000002</v>
       </c>
-      <c r="G130" s="9">
+      <c r="G130" s="7">
         <v>3.3</v>
       </c>
       <c r="H130" s="2">
@@ -5342,11 +6457,20 @@
       <c r="I130" s="2">
         <v>3.2</v>
       </c>
-      <c r="J130" s="10">
+      <c r="J130" s="9">
         <v>1.9301999999999999</v>
       </c>
-    </row>
-    <row r="131" spans="1:10">
+      <c r="K130" s="10">
+        <v>1.6130442700000001</v>
+      </c>
+      <c r="L130" s="12">
+        <v>1.5608402699999999</v>
+      </c>
+      <c r="M130" s="13">
+        <v>2.03487537</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13">
       <c r="A131" t="s">
         <v>211</v>
       </c>
@@ -5365,7 +6489,7 @@
       <c r="F131" s="8">
         <v>102.893</v>
       </c>
-      <c r="G131" s="9">
+      <c r="G131" s="7">
         <v>2.8</v>
       </c>
       <c r="H131" s="2">
@@ -5374,11 +6498,20 @@
       <c r="I131" s="2">
         <v>3.5</v>
       </c>
-      <c r="J131" s="10">
+      <c r="J131" s="9">
         <v>1.7483</v>
       </c>
-    </row>
-    <row r="132" spans="1:10">
+      <c r="K131" s="10">
+        <v>1.5757360300000001</v>
+      </c>
+      <c r="L131" s="12">
+        <v>1.4449727000000001</v>
+      </c>
+      <c r="M131" s="13">
+        <v>2.0140042299999998</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13">
       <c r="A132" t="s">
         <v>212</v>
       </c>
@@ -5397,7 +6530,7 @@
       <c r="F132" s="8">
         <v>93.48</v>
       </c>
-      <c r="G132" s="9">
+      <c r="G132" s="7">
         <v>1.9</v>
       </c>
       <c r="H132" s="2">
@@ -5406,11 +6539,20 @@
       <c r="I132" s="2">
         <v>3.1</v>
       </c>
-      <c r="J132" s="10">
+      <c r="J132" s="9">
         <v>1.9376</v>
       </c>
-    </row>
-    <row r="133" spans="1:10">
+      <c r="K132" s="10">
+        <v>1.5402332299999999</v>
+      </c>
+      <c r="L132" s="12">
+        <v>1.3555188199999999</v>
+      </c>
+      <c r="M132" s="13">
+        <v>1.99262947</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13">
       <c r="A133" t="s">
         <v>213</v>
       </c>
@@ -5429,7 +6571,7 @@
       <c r="F133" s="8">
         <v>92.27</v>
       </c>
-      <c r="G133" s="9">
+      <c r="G133" s="7">
         <v>1.7</v>
       </c>
       <c r="H133" s="2">
@@ -5438,11 +6580,20 @@
       <c r="I133" s="2">
         <v>3.3</v>
       </c>
-      <c r="J133" s="10">
+      <c r="J133" s="9">
         <v>1.8588</v>
       </c>
-    </row>
-    <row r="134" spans="1:10">
+      <c r="K133" s="10">
+        <v>1.4983123700000001</v>
+      </c>
+      <c r="L133" s="12">
+        <v>1.5327489000000001</v>
+      </c>
+      <c r="M133" s="13">
+        <v>1.9582028</v>
+      </c>
+    </row>
+    <row r="134" spans="1:13">
       <c r="A134" t="s">
         <v>214</v>
       </c>
@@ -5461,7 +6612,7 @@
       <c r="F134" s="8">
         <v>88.16</v>
       </c>
-      <c r="G134" s="9">
+      <c r="G134" s="7">
         <v>1.9</v>
       </c>
       <c r="H134" s="2">
@@ -5470,11 +6621,20 @@
       <c r="I134" s="2">
         <v>3.1</v>
       </c>
-      <c r="J134" s="10">
+      <c r="J134" s="9">
         <v>1.9932000000000001</v>
       </c>
-    </row>
-    <row r="135" spans="1:10">
+      <c r="K134" s="10">
+        <v>1.5156210299999999</v>
+      </c>
+      <c r="L134" s="12">
+        <v>1.79308003</v>
+      </c>
+      <c r="M134" s="13">
+        <v>1.9603714999999999</v>
+      </c>
+    </row>
+    <row r="135" spans="1:13">
       <c r="A135" t="s">
         <v>215</v>
       </c>
@@ -5493,7 +6653,7 @@
       <c r="F135" s="8">
         <v>94.352999999999994</v>
       </c>
-      <c r="G135" s="9">
+      <c r="G135" s="7">
         <v>1.7</v>
       </c>
       <c r="H135" s="2">
@@ -5502,11 +6662,20 @@
       <c r="I135" s="2">
         <v>3.3</v>
       </c>
-      <c r="J135" s="10">
+      <c r="J135" s="9">
         <v>1.9262999999999999</v>
       </c>
-    </row>
-    <row r="136" spans="1:10">
+      <c r="K135" s="10">
+        <v>1.4797121</v>
+      </c>
+      <c r="L135" s="12">
+        <v>1.2271109</v>
+      </c>
+      <c r="M135" s="13">
+        <v>1.9555777700000001</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13">
       <c r="A136" t="s">
         <v>216</v>
       </c>
@@ -5525,7 +6694,7 @@
       <c r="F136" s="8">
         <v>94.222999999999999</v>
       </c>
-      <c r="G136" s="9">
+      <c r="G136" s="7">
         <v>1.4</v>
       </c>
       <c r="H136" s="2">
@@ -5534,11 +6703,20 @@
       <c r="I136" s="2">
         <v>3.1</v>
       </c>
-      <c r="J136" s="10">
+      <c r="J136" s="9">
         <v>1.8684000000000001</v>
       </c>
-    </row>
-    <row r="137" spans="1:10">
+      <c r="K136" s="10">
+        <v>1.4753455</v>
+      </c>
+      <c r="L136" s="12">
+        <v>1.3291835299999999</v>
+      </c>
+      <c r="M136" s="13">
+        <v>1.9495149300000001</v>
+      </c>
+    </row>
+    <row r="137" spans="1:13">
       <c r="A137" t="s">
         <v>217</v>
       </c>
@@ -5557,7 +6735,7 @@
       <c r="F137" s="8">
         <v>105.82299999999999</v>
       </c>
-      <c r="G137" s="9">
+      <c r="G137" s="7">
         <v>1.5</v>
       </c>
       <c r="H137" s="2">
@@ -5566,11 +6744,20 @@
       <c r="I137" s="2">
         <v>3.1</v>
       </c>
-      <c r="J137" s="10">
+      <c r="J137" s="9">
         <v>1.8130999999999999</v>
       </c>
-    </row>
-    <row r="138" spans="1:10">
+      <c r="K137" s="10">
+        <v>1.7538161000000001</v>
+      </c>
+      <c r="L137" s="12">
+        <v>1.6676276299999999</v>
+      </c>
+      <c r="M137" s="13">
+        <v>2.1226365999999999</v>
+      </c>
+    </row>
+    <row r="138" spans="1:13">
       <c r="A138" t="s">
         <v>218</v>
       </c>
@@ -5589,7 +6776,7 @@
       <c r="F138" s="8">
         <v>97.343000000000004</v>
       </c>
-      <c r="G138" s="9">
+      <c r="G138" s="7">
         <v>1.2</v>
       </c>
       <c r="H138" s="2">
@@ -5598,11 +6785,20 @@
       <c r="I138" s="2">
         <v>3</v>
       </c>
-      <c r="J138" s="10">
+      <c r="J138" s="9">
         <v>1.8067</v>
       </c>
-    </row>
-    <row r="139" spans="1:10">
+      <c r="K138" s="10">
+        <v>1.7420456</v>
+      </c>
+      <c r="L138" s="12">
+        <v>1.6433769</v>
+      </c>
+      <c r="M138" s="13">
+        <v>2.1154151300000001</v>
+      </c>
+    </row>
+    <row r="139" spans="1:13">
       <c r="A139" t="s">
         <v>219</v>
       </c>
@@ -5621,7 +6817,7 @@
       <c r="F139" s="8">
         <v>98.747</v>
       </c>
-      <c r="G139" s="9">
+      <c r="G139" s="7">
         <v>1.4</v>
       </c>
       <c r="H139" s="2">
@@ -5630,11 +6826,20 @@
       <c r="I139" s="2">
         <v>3.2</v>
       </c>
-      <c r="J139" s="10">
+      <c r="J139" s="9">
         <v>1.8391999999999999</v>
       </c>
-    </row>
-    <row r="140" spans="1:10">
+      <c r="K139" s="10">
+        <v>1.78776157</v>
+      </c>
+      <c r="L139" s="12">
+        <v>1.4811783700000001</v>
+      </c>
+      <c r="M139" s="13">
+        <v>2.15238387</v>
+      </c>
+    </row>
+    <row r="140" spans="1:13">
       <c r="A140" t="s">
         <v>220</v>
       </c>
@@ -5653,7 +6858,7 @@
       <c r="F140" s="8">
         <v>103.34699999999999</v>
       </c>
-      <c r="G140" s="9">
+      <c r="G140" s="7">
         <v>2.1</v>
       </c>
       <c r="H140" s="2">
@@ -5662,11 +6867,20 @@
       <c r="I140" s="2">
         <v>3.2</v>
       </c>
-      <c r="J140" s="10">
+      <c r="J140" s="9">
         <v>1.8751</v>
       </c>
-    </row>
-    <row r="141" spans="1:10">
+      <c r="K140" s="10">
+        <v>1.8579101</v>
+      </c>
+      <c r="L140" s="12">
+        <v>1.6493156</v>
+      </c>
+      <c r="M140" s="13">
+        <v>2.1928181000000002</v>
+      </c>
+    </row>
+    <row r="141" spans="1:13">
       <c r="A141" t="s">
         <v>221</v>
       </c>
@@ -5685,7 +6899,7 @@
       <c r="F141" s="8">
         <v>97.78</v>
       </c>
-      <c r="G141" s="9">
+      <c r="G141" s="7">
         <v>1.8</v>
       </c>
       <c r="H141" s="2">
@@ -5694,11 +6908,20 @@
       <c r="I141" s="2">
         <v>3.2</v>
       </c>
-      <c r="J141" s="10">
+      <c r="J141" s="9">
         <v>1.966</v>
       </c>
-    </row>
-    <row r="142" spans="1:10">
+      <c r="K141" s="10">
+        <v>1.89152437</v>
+      </c>
+      <c r="L141" s="12">
+        <v>1.9270282299999999</v>
+      </c>
+      <c r="M141" s="13">
+        <v>2.2047213000000001</v>
+      </c>
+    </row>
+    <row r="142" spans="1:13">
       <c r="A142" t="s">
         <v>222</v>
       </c>
@@ -5717,7 +6940,7 @@
       <c r="F142" s="8">
         <v>73.16</v>
       </c>
-      <c r="G142" s="9">
+      <c r="G142" s="7">
         <v>1.2</v>
       </c>
       <c r="H142" s="2">
@@ -5726,11 +6949,20 @@
       <c r="I142" s="2">
         <v>2.8</v>
       </c>
-      <c r="J142" s="10">
+      <c r="J142" s="9">
         <v>1.8653999999999999</v>
       </c>
-    </row>
-    <row r="143" spans="1:10">
+      <c r="K142" s="10">
+        <v>1.8468636</v>
+      </c>
+      <c r="L142" s="12">
+        <v>1.7031663699999999</v>
+      </c>
+      <c r="M142" s="13">
+        <v>2.1819615300000001</v>
+      </c>
+    </row>
+    <row r="143" spans="1:13">
       <c r="A143" t="s">
         <v>223</v>
       </c>
@@ -5749,7 +6981,7 @@
       <c r="F143" s="8">
         <v>48.54</v>
       </c>
-      <c r="G143" s="9">
+      <c r="G143" s="7">
         <v>-0.1</v>
       </c>
       <c r="H143" s="2">
@@ -5758,11 +6990,20 @@
       <c r="I143" s="2">
         <v>2.8</v>
       </c>
-      <c r="J143" s="10">
+      <c r="J143" s="9">
         <v>1.7706999999999999</v>
       </c>
-    </row>
-    <row r="144" spans="1:10">
+      <c r="K143" s="10">
+        <v>1.64393677</v>
+      </c>
+      <c r="L143" s="12">
+        <v>0.69927391000000005</v>
+      </c>
+      <c r="M143" s="13">
+        <v>2.0790921999999998</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13">
       <c r="A144" t="s">
         <v>224</v>
       </c>
@@ -5781,7 +7022,7 @@
       <c r="F144" s="8">
         <v>57.847000000000001</v>
       </c>
-      <c r="G144" s="9">
+      <c r="G144" s="7">
         <v>0</v>
       </c>
       <c r="H144" s="2">
@@ -5790,11 +7031,20 @@
       <c r="I144" s="2">
         <v>2.7</v>
       </c>
-      <c r="J144" s="10">
+      <c r="J144" s="9">
         <v>1.8144</v>
       </c>
-    </row>
-    <row r="145" spans="1:10">
+      <c r="K144" s="10">
+        <v>1.7766960000000001</v>
+      </c>
+      <c r="L144" s="12">
+        <v>1.6892917000000001</v>
+      </c>
+      <c r="M144" s="13">
+        <v>2.13530313</v>
+      </c>
+    </row>
+    <row r="145" spans="1:13">
       <c r="A145" t="s">
         <v>225</v>
       </c>
@@ -5813,7 +7063,7 @@
       <c r="F145" s="8">
         <v>46.417000000000002</v>
       </c>
-      <c r="G145" s="9">
+      <c r="G145" s="7">
         <v>0.2</v>
       </c>
       <c r="H145" s="2">
@@ -5822,11 +7072,20 @@
       <c r="I145" s="2">
         <v>2.8</v>
       </c>
-      <c r="J145" s="10">
+      <c r="J145" s="9">
         <v>1.7656000000000001</v>
       </c>
-    </row>
-    <row r="146" spans="1:10">
+      <c r="K145" s="10">
+        <v>1.84644305</v>
+      </c>
+      <c r="L145" s="12">
+        <v>1.81809318</v>
+      </c>
+      <c r="M145" s="13">
+        <v>2.1780345400000001</v>
+      </c>
+    </row>
+    <row r="146" spans="1:13">
       <c r="A146" t="s">
         <v>226</v>
       </c>
@@ -5845,7 +7104,7 @@
       <c r="F146" s="8">
         <v>41.95</v>
       </c>
-      <c r="G146" s="9">
+      <c r="G146" s="7">
         <v>0.4</v>
       </c>
       <c r="H146" s="2">
@@ -5854,11 +7113,20 @@
       <c r="I146" s="2">
         <v>2.7</v>
       </c>
-      <c r="J146" s="10">
+      <c r="J146" s="9">
         <v>1.8526</v>
       </c>
-    </row>
-    <row r="147" spans="1:10">
+      <c r="K146" s="10">
+        <v>1.78608411</v>
+      </c>
+      <c r="L146" s="12">
+        <v>1.3622015199999999</v>
+      </c>
+      <c r="M146" s="13">
+        <v>2.1543001899999998</v>
+      </c>
+    </row>
+    <row r="147" spans="1:13">
       <c r="A147" t="s">
         <v>227</v>
       </c>
@@ -5877,7 +7145,7 @@
       <c r="F147" s="8">
         <v>33.183</v>
       </c>
-      <c r="G147" s="9">
+      <c r="G147" s="7">
         <v>1</v>
       </c>
       <c r="H147" s="2">
@@ -5886,11 +7154,20 @@
       <c r="I147" s="2">
         <v>2.6</v>
       </c>
-      <c r="J147" s="10">
+      <c r="J147" s="9">
         <v>1.8085</v>
       </c>
-    </row>
-    <row r="148" spans="1:10">
+      <c r="K147" s="10">
+        <v>1.7355012599999999</v>
+      </c>
+      <c r="L147" s="12">
+        <v>1.12437571</v>
+      </c>
+      <c r="M147" s="13">
+        <v>2.1286194200000002</v>
+      </c>
+    </row>
+    <row r="148" spans="1:13">
       <c r="A148" t="s">
         <v>228</v>
       </c>
@@ -5909,7 +7186,7 @@
       <c r="F148" s="8">
         <v>45.406999999999996</v>
       </c>
-      <c r="G148" s="9">
+      <c r="G148" s="7">
         <v>1.1000000000000001</v>
       </c>
       <c r="H148" s="2">
@@ -5918,11 +7195,20 @@
       <c r="I148" s="2">
         <v>2.6</v>
       </c>
-      <c r="J148" s="10">
+      <c r="J148" s="9">
         <v>1.8686</v>
       </c>
-    </row>
-    <row r="149" spans="1:10">
+      <c r="K148" s="10">
+        <v>1.7295723300000001</v>
+      </c>
+      <c r="L148" s="12">
+        <v>1.5436493899999999</v>
+      </c>
+      <c r="M148" s="13">
+        <v>2.1092469199999999</v>
+      </c>
+    </row>
+    <row r="149" spans="1:13">
       <c r="A149" t="s">
         <v>229</v>
       </c>
@@ -5941,7 +7227,7 @@
       <c r="F149" s="8">
         <v>44.85</v>
       </c>
-      <c r="G149" s="9">
+      <c r="G149" s="7">
         <v>1.2</v>
       </c>
       <c r="H149" s="2">
@@ -5950,11 +7236,20 @@
       <c r="I149" s="2">
         <v>2.5</v>
       </c>
-      <c r="J149" s="10">
+      <c r="J149" s="9">
         <v>1.8892</v>
       </c>
-    </row>
-    <row r="150" spans="1:10">
+      <c r="K149" s="10">
+        <v>1.66854375</v>
+      </c>
+      <c r="L149" s="12">
+        <v>1.76755273</v>
+      </c>
+      <c r="M149" s="13">
+        <v>2.0625139899999998</v>
+      </c>
+    </row>
+    <row r="150" spans="1:13">
       <c r="A150" t="s">
         <v>230</v>
       </c>
@@ -5973,7 +7268,7 @@
       <c r="F150" s="8">
         <v>49.137</v>
       </c>
-      <c r="G150" s="9">
+      <c r="G150" s="7">
         <v>1.8</v>
       </c>
       <c r="H150" s="2">
@@ -5982,11 +7277,20 @@
       <c r="I150" s="2">
         <v>2.2999999999999998</v>
       </c>
-      <c r="J150" s="10">
+      <c r="J150" s="9">
         <v>1.9401999999999999</v>
       </c>
-    </row>
-    <row r="151" spans="1:10">
+      <c r="K150" s="10">
+        <v>1.8055258300000001</v>
+      </c>
+      <c r="L150" s="12">
+        <v>1.9793107999999999</v>
+      </c>
+      <c r="M150" s="13">
+        <v>2.1460168500000001</v>
+      </c>
+    </row>
+    <row r="151" spans="1:13">
       <c r="A151" t="s">
         <v>231</v>
       </c>
@@ -6005,7 +7309,7 @@
       <c r="F151" s="8">
         <v>51.767000000000003</v>
       </c>
-      <c r="G151" s="9">
+      <c r="G151" s="7">
         <v>2.6</v>
       </c>
       <c r="H151" s="2">
@@ -6014,11 +7318,20 @@
       <c r="I151" s="2">
         <v>2.6</v>
       </c>
-      <c r="J151" s="10">
+      <c r="J151" s="9">
         <v>2.1025</v>
       </c>
-    </row>
-    <row r="152" spans="1:10">
+      <c r="K151" s="10">
+        <v>1.91043834</v>
+      </c>
+      <c r="L151" s="12">
+        <v>1.84955124</v>
+      </c>
+      <c r="M151" s="13">
+        <v>2.21682969</v>
+      </c>
+    </row>
+    <row r="152" spans="1:13">
       <c r="A152" t="s">
         <v>232</v>
       </c>
@@ -6037,7 +7350,7 @@
       <c r="F152" s="8">
         <v>48.24</v>
       </c>
-      <c r="G152" s="9">
+      <c r="G152" s="7">
         <v>1.9</v>
       </c>
       <c r="H152" s="2">
@@ -6046,11 +7359,20 @@
       <c r="I152" s="2">
         <v>2.6</v>
       </c>
-      <c r="J152" s="10">
+      <c r="J152" s="9">
         <v>2.0102000000000002</v>
       </c>
-    </row>
-    <row r="153" spans="1:10">
+      <c r="K152" s="10">
+        <v>1.8094428899999999</v>
+      </c>
+      <c r="L152" s="12">
+        <v>1.4140546000000001</v>
+      </c>
+      <c r="M152" s="13">
+        <v>2.1636756500000001</v>
+      </c>
+    </row>
+    <row r="153" spans="1:13">
       <c r="A153" t="s">
         <v>233</v>
       </c>
@@ -6069,7 +7391,7 @@
       <c r="F153" s="8">
         <v>48.162999999999997</v>
       </c>
-      <c r="G153" s="9">
+      <c r="G153" s="7">
         <v>1.9</v>
       </c>
       <c r="H153" s="2">
@@ -6078,11 +7400,20 @@
       <c r="I153" s="2">
         <v>2.6</v>
       </c>
-      <c r="J153" s="10">
+      <c r="J153" s="9">
         <v>1.9432</v>
       </c>
-    </row>
-    <row r="154" spans="1:10">
+      <c r="K153" s="10">
+        <v>1.8362551300000001</v>
+      </c>
+      <c r="L153" s="12">
+        <v>1.80738007</v>
+      </c>
+      <c r="M153" s="13">
+        <v>2.1671786499999999</v>
+      </c>
+    </row>
+    <row r="154" spans="1:13">
       <c r="A154" t="s">
         <v>234</v>
       </c>
@@ -6101,7 +7432,7 @@
       <c r="F154" s="8">
         <v>55.366999999999997</v>
       </c>
-      <c r="G154" s="9">
+      <c r="G154" s="7">
         <v>2.1</v>
       </c>
       <c r="H154" s="2">
@@ -6110,11 +7441,20 @@
       <c r="I154" s="2">
         <v>2.5</v>
       </c>
-      <c r="J154" s="10">
+      <c r="J154" s="9">
         <v>1.998</v>
       </c>
-    </row>
-    <row r="155" spans="1:10">
+      <c r="K154" s="10">
+        <v>1.9430470799999999</v>
+      </c>
+      <c r="L154" s="12">
+        <v>2.2819830400000001</v>
+      </c>
+      <c r="M154" s="13">
+        <v>2.22117421</v>
+      </c>
+    </row>
+    <row r="155" spans="1:13">
       <c r="A155" t="s">
         <v>235</v>
       </c>
@@ -6133,7 +7473,7 @@
       <c r="F155" s="8">
         <v>62.887</v>
       </c>
-      <c r="G155" s="9">
+      <c r="G155" s="7">
         <v>2.2000000000000002</v>
       </c>
       <c r="H155" s="2">
@@ -6142,11 +7482,20 @@
       <c r="I155" s="2">
         <v>2.7</v>
       </c>
-      <c r="J155" s="10">
+      <c r="J155" s="9">
         <v>2.0365000000000002</v>
       </c>
-    </row>
-    <row r="156" spans="1:10">
+      <c r="K155" s="10">
+        <v>1.99999744</v>
+      </c>
+      <c r="L155" s="12">
+        <v>1.9105596899999999</v>
+      </c>
+      <c r="M155" s="13">
+        <v>2.27018144</v>
+      </c>
+    </row>
+    <row r="156" spans="1:13">
       <c r="A156" t="s">
         <v>236</v>
       </c>
@@ -6165,7 +7514,7 @@
       <c r="F156" s="8">
         <v>68.033000000000001</v>
       </c>
-      <c r="G156" s="9">
+      <c r="G156" s="7">
         <v>2.7</v>
       </c>
       <c r="H156" s="2">
@@ -6174,11 +7523,20 @@
       <c r="I156" s="2">
         <v>2.8</v>
       </c>
-      <c r="J156" s="10">
+      <c r="J156" s="9">
         <v>2.1011000000000002</v>
       </c>
-    </row>
-    <row r="157" spans="1:10">
+      <c r="K156" s="10">
+        <v>2.0406281399999999</v>
+      </c>
+      <c r="L156" s="12">
+        <v>1.8018564800000001</v>
+      </c>
+      <c r="M156" s="13">
+        <v>2.2993429399999998</v>
+      </c>
+    </row>
+    <row r="157" spans="1:13">
       <c r="A157">
         <v>20183</v>
       </c>
@@ -6197,7 +7555,7 @@
       <c r="F157" s="8">
         <v>69.757000000000005</v>
       </c>
-      <c r="G157" s="9">
+      <c r="G157" s="7">
         <v>2.6</v>
       </c>
       <c r="H157" s="2">
@@ -6206,11 +7564,20 @@
       <c r="I157" s="2">
         <v>2.9</v>
       </c>
-      <c r="J157" s="10">
+      <c r="J157" s="9">
         <v>2.2248999999999999</v>
       </c>
-    </row>
-    <row r="158" spans="1:10">
+      <c r="K157" s="10">
+        <v>2.1240775699999999</v>
+      </c>
+      <c r="L157" s="12">
+        <v>2.22052067</v>
+      </c>
+      <c r="M157" s="13">
+        <v>2.3392902800000002</v>
+      </c>
+    </row>
+    <row r="158" spans="1:13">
       <c r="A158">
         <v>20184</v>
       </c>
@@ -6229,7 +7596,7 @@
       <c r="F158" s="8">
         <v>59.076999999999998</v>
       </c>
-      <c r="G158" s="9">
+      <c r="G158" s="7">
         <v>2.2000000000000002</v>
       </c>
       <c r="H158" s="2">
@@ -6238,11 +7605,20 @@
       <c r="I158" s="2">
         <v>2.8</v>
       </c>
-      <c r="J158" s="10">
+      <c r="J158" s="9">
         <v>2.2151000000000001</v>
       </c>
-    </row>
-    <row r="159" spans="1:10">
+      <c r="K158" s="10">
+        <v>2.1374345799999999</v>
+      </c>
+      <c r="L158" s="12">
+        <v>2.1200842799999999</v>
+      </c>
+      <c r="M158" s="13">
+        <v>2.34979256</v>
+      </c>
+    </row>
+    <row r="159" spans="1:13">
       <c r="A159">
         <v>20191</v>
       </c>
@@ -6261,7 +7637,7 @@
       <c r="F159" s="8">
         <v>54.826999999999998</v>
       </c>
-      <c r="G159" s="9">
+      <c r="G159" s="7">
         <v>1.6</v>
       </c>
       <c r="H159" s="2">
@@ -6270,11 +7646,20 @@
       <c r="I159" s="2">
         <v>2.6</v>
       </c>
-      <c r="J159" s="10">
+      <c r="J159" s="9">
         <v>2.1038000000000001</v>
       </c>
-    </row>
-    <row r="160" spans="1:10">
+      <c r="K159" s="10">
+        <v>1.87369886</v>
+      </c>
+      <c r="L159" s="12">
+        <v>1.6562379199999999</v>
+      </c>
+      <c r="M159" s="13">
+        <v>2.1905942500000002</v>
+      </c>
+    </row>
+    <row r="160" spans="1:13">
       <c r="A160">
         <v>20192</v>
       </c>
@@ -6293,7 +7678,7 @@
       <c r="F160" s="8">
         <v>59.783000000000001</v>
       </c>
-      <c r="G160" s="9">
+      <c r="G160" s="7">
         <v>1.8</v>
       </c>
       <c r="H160" s="2">
@@ -6302,11 +7687,20 @@
       <c r="I160" s="2">
         <v>2.7</v>
       </c>
-      <c r="J160" s="10">
+      <c r="J160" s="9">
         <v>2.0131000000000001</v>
       </c>
-    </row>
-    <row r="161" spans="1:10">
+      <c r="K160" s="10">
+        <v>1.72902869</v>
+      </c>
+      <c r="L160" s="12">
+        <v>1.94388687</v>
+      </c>
+      <c r="M160" s="13">
+        <v>2.0845739499999998</v>
+      </c>
+    </row>
+    <row r="161" spans="1:13">
       <c r="A161">
         <v>20193</v>
       </c>
@@ -6325,7 +7719,7 @@
       <c r="F161" s="8">
         <v>56.37</v>
       </c>
-      <c r="G161" s="9">
+      <c r="G161" s="7">
         <v>1.7</v>
       </c>
       <c r="H161" s="2">
@@ -6334,11 +7728,20 @@
       <c r="I161" s="2">
         <v>2.7</v>
       </c>
-      <c r="J161" s="10">
+      <c r="J161" s="9">
         <v>1.9786999999999999</v>
       </c>
-    </row>
-    <row r="162" spans="1:10">
+      <c r="K161" s="10">
+        <v>1.63188092</v>
+      </c>
+      <c r="L161" s="12">
+        <v>1.70230685</v>
+      </c>
+      <c r="M161" s="13">
+        <v>2.0313527200000001</v>
+      </c>
+    </row>
+    <row r="162" spans="1:13">
       <c r="A162">
         <v>20194</v>
       </c>
@@ -6357,7 +7760,7 @@
       <c r="F162" s="8">
         <v>56.957000000000001</v>
       </c>
-      <c r="G162" s="9">
+      <c r="G162" s="7">
         <v>2</v>
       </c>
       <c r="H162" s="2">
@@ -6366,11 +7769,20 @@
       <c r="I162" s="2">
         <v>2.4</v>
       </c>
-      <c r="J162" s="10">
+      <c r="J162" s="9">
         <v>1.9404999999999999</v>
       </c>
-    </row>
-    <row r="163" spans="1:10">
+      <c r="K162" s="10">
+        <v>1.6786218500000001</v>
+      </c>
+      <c r="L162" s="12">
+        <v>1.7085620100000001</v>
+      </c>
+      <c r="M162" s="13">
+        <v>2.0644794700000002</v>
+      </c>
+    </row>
+    <row r="163" spans="1:13">
       <c r="A163">
         <v>20201</v>
       </c>
@@ -6389,7 +7801,7 @@
       <c r="F163" s="8">
         <v>45.756999999999998</v>
       </c>
-      <c r="G163" s="9">
+      <c r="G163" s="7">
         <v>2.1</v>
       </c>
       <c r="H163" s="2">
@@ -6398,11 +7810,20 @@
       <c r="I163" s="2">
         <v>2.4</v>
       </c>
-      <c r="J163" s="10">
+      <c r="J163" s="9">
         <v>1.9268000000000001</v>
       </c>
-    </row>
-    <row r="164" spans="1:10">
+      <c r="K163" s="10">
+        <v>1.54115205</v>
+      </c>
+      <c r="L163" s="12">
+        <v>1.4767156299999999</v>
+      </c>
+      <c r="M163" s="13">
+        <v>1.98076272</v>
+      </c>
+    </row>
+    <row r="164" spans="1:13">
       <c r="A164">
         <v>20202</v>
       </c>
@@ -6421,7 +7842,7 @@
       <c r="F164" s="8">
         <v>27.806999999999999</v>
       </c>
-      <c r="G164" s="9">
+      <c r="G164" s="7">
         <v>0.4</v>
       </c>
       <c r="H164" s="2">
@@ -6430,11 +7851,20 @@
       <c r="I164" s="2">
         <v>2.8</v>
       </c>
-      <c r="J164" s="10">
+      <c r="J164" s="9">
         <v>1.3731</v>
       </c>
-    </row>
-    <row r="165" spans="1:10">
+      <c r="K164" s="10">
+        <v>1.1841864099999999</v>
+      </c>
+      <c r="L164" s="12">
+        <v>8.1204360000000003E-2</v>
+      </c>
+      <c r="M164" s="13">
+        <v>1.79646803</v>
+      </c>
+    </row>
+    <row r="165" spans="1:13">
       <c r="A165">
         <v>20203</v>
       </c>
@@ -6453,7 +7883,7 @@
       <c r="F165" s="8">
         <v>40.893000000000001</v>
       </c>
-      <c r="G165" s="9">
+      <c r="G165" s="7">
         <v>1.2</v>
       </c>
       <c r="H165" s="2">
@@ -6462,11 +7892,20 @@
       <c r="I165" s="2">
         <v>2.9</v>
       </c>
-      <c r="J165" s="10">
+      <c r="J165" s="9">
         <v>1.5176000000000001</v>
       </c>
-    </row>
-    <row r="166" spans="1:10">
+      <c r="K165" s="10">
+        <v>1.34628517</v>
+      </c>
+      <c r="L165" s="12">
+        <v>1.61051254</v>
+      </c>
+      <c r="M165" s="13">
+        <v>1.85257351</v>
+      </c>
+    </row>
+    <row r="166" spans="1:13">
       <c r="A166">
         <v>20204</v>
       </c>
@@ -6485,7 +7924,7 @@
       <c r="F166" s="8">
         <v>42.453000000000003</v>
       </c>
-      <c r="G166" s="9">
+      <c r="G166" s="7">
         <v>1.2</v>
       </c>
       <c r="H166" s="2">
@@ -6494,11 +7933,20 @@
       <c r="I166" s="2">
         <v>2.6</v>
       </c>
-      <c r="J166" s="10">
+      <c r="J166" s="9">
         <v>1.8720000000000001</v>
       </c>
-    </row>
-    <row r="167" spans="1:10">
+      <c r="K166" s="10">
+        <v>1.3771135800000001</v>
+      </c>
+      <c r="L166" s="12">
+        <v>1.4888628100000001</v>
+      </c>
+      <c r="M166" s="13">
+        <v>1.8795095100000001</v>
+      </c>
+    </row>
+    <row r="167" spans="1:13">
       <c r="A167">
         <v>20211</v>
       </c>
@@ -6517,7 +7965,7 @@
       <c r="F167" s="8">
         <v>57.79</v>
       </c>
-      <c r="G167" s="9">
+      <c r="G167" s="7">
         <v>1.9</v>
       </c>
       <c r="H167" s="2">
@@ -6526,11 +7974,20 @@
       <c r="I167" s="2">
         <v>3.1</v>
       </c>
-      <c r="J167" s="10">
+      <c r="J167" s="9">
         <v>1.9533</v>
       </c>
-    </row>
-    <row r="168" spans="1:10">
+      <c r="K167" s="10">
+        <v>1.43480114</v>
+      </c>
+      <c r="L167" s="12">
+        <v>1.54513912</v>
+      </c>
+      <c r="M167" s="13">
+        <v>1.9164282500000001</v>
+      </c>
+    </row>
+    <row r="168" spans="1:13">
       <c r="A168">
         <v>20212</v>
       </c>
@@ -6549,7 +8006,7 @@
       <c r="F168" s="8">
         <v>66.09</v>
       </c>
-      <c r="G168" s="9">
+      <c r="G168" s="7">
         <v>4.8</v>
       </c>
       <c r="H168" s="2">
@@ -6558,11 +8015,20 @@
       <c r="I168" s="2">
         <v>4.0999999999999996</v>
       </c>
-      <c r="J168" s="10">
+      <c r="J168" s="9">
         <v>2.3090999999999999</v>
       </c>
-    </row>
-    <row r="169" spans="1:10">
+      <c r="K168" s="10">
+        <v>1.58592953</v>
+      </c>
+      <c r="L168" s="12">
+        <v>1.89270443</v>
+      </c>
+      <c r="M168" s="13">
+        <v>2.0020693600000001</v>
+      </c>
+    </row>
+    <row r="169" spans="1:13">
       <c r="A169">
         <v>20213</v>
       </c>
@@ -6581,7 +8047,7 @@
       <c r="F169" s="8">
         <v>70.623000000000005</v>
       </c>
-      <c r="G169" s="9">
+      <c r="G169" s="7">
         <v>5.3</v>
       </c>
       <c r="H169" s="2">
@@ -6590,11 +8056,20 @@
       <c r="I169" s="2">
         <v>4.5999999999999996</v>
       </c>
-      <c r="J169" s="10">
+      <c r="J169" s="9">
         <v>2.2511999999999999</v>
       </c>
-    </row>
-    <row r="170" spans="1:10">
+      <c r="K169" s="10">
+        <v>1.6159198699999999</v>
+      </c>
+      <c r="L169" s="12">
+        <v>2.4065552800000001</v>
+      </c>
+      <c r="M169" s="13">
+        <v>2.0052823200000001</v>
+      </c>
+    </row>
+    <row r="170" spans="1:13">
       <c r="A170">
         <v>20214</v>
       </c>
@@ -6613,7 +8088,7 @@
       <c r="F170" s="8">
         <v>77.447000000000003</v>
       </c>
-      <c r="G170" s="9">
+      <c r="G170" s="7">
         <v>6.8</v>
       </c>
       <c r="H170" s="2">
@@ -6622,11 +8097,20 @@
       <c r="I170" s="2">
         <v>4.8</v>
       </c>
-      <c r="J170" s="10">
+      <c r="J170" s="9">
         <v>2.5708000000000002</v>
       </c>
-    </row>
-    <row r="171" spans="1:10">
+      <c r="K170" s="10">
+        <v>1.7100703500000001</v>
+      </c>
+      <c r="L170" s="12">
+        <v>2.3181722200000001</v>
+      </c>
+      <c r="M170" s="13">
+        <v>2.0698820100000002</v>
+      </c>
+    </row>
+    <row r="171" spans="1:13">
       <c r="A171">
         <v>20221</v>
       </c>
@@ -6645,7 +8129,7 @@
       <c r="F171" s="8">
         <v>94.453000000000003</v>
       </c>
-      <c r="G171" s="9">
+      <c r="G171" s="7">
         <v>8</v>
       </c>
       <c r="H171" s="2">
@@ -6654,11 +8138,20 @@
       <c r="I171" s="2">
         <v>5.0999999999999996</v>
       </c>
-      <c r="J171" s="10">
+      <c r="J171" s="9">
         <v>2.8054000000000001</v>
       </c>
-    </row>
-    <row r="172" spans="1:10">
+      <c r="K171" s="10">
+        <v>1.88830053</v>
+      </c>
+      <c r="L171" s="12">
+        <v>2.64229205</v>
+      </c>
+      <c r="M171" s="13">
+        <v>2.17571827</v>
+      </c>
+    </row>
+    <row r="172" spans="1:13">
       <c r="A172">
         <v>20222</v>
       </c>
@@ -6677,7 +8170,7 @@
       <c r="F172" s="8">
         <v>108.723</v>
       </c>
-      <c r="G172" s="9">
+      <c r="G172" s="7">
         <v>8.6</v>
       </c>
       <c r="H172" s="2">
@@ -6686,11 +8179,20 @@
       <c r="I172" s="2">
         <v>5.3</v>
       </c>
-      <c r="J172" s="10">
+      <c r="J172" s="9">
         <v>3.0388000000000002</v>
       </c>
-    </row>
-    <row r="173" spans="1:10">
+      <c r="K172" s="10">
+        <v>2.3276375200000001</v>
+      </c>
+      <c r="L172" s="12">
+        <v>3.7514248800000001</v>
+      </c>
+      <c r="M172" s="13">
+        <v>2.4245064900000002</v>
+      </c>
+    </row>
+    <row r="173" spans="1:13">
       <c r="A173">
         <v>20223</v>
       </c>
@@ -6709,7 +8211,7 @@
       <c r="F173" s="8">
         <v>93.183000000000007</v>
       </c>
-      <c r="G173" s="9">
+      <c r="G173" s="7">
         <v>8.3000000000000007</v>
       </c>
       <c r="H173" s="2">
@@ -6718,11 +8220,20 @@
       <c r="I173" s="2">
         <v>4.9000000000000004</v>
       </c>
-      <c r="J173" s="10">
+      <c r="J173" s="9">
         <v>3.0528</v>
       </c>
-    </row>
-    <row r="174" spans="1:10">
+      <c r="K173" s="10">
+        <v>2.22938466</v>
+      </c>
+      <c r="L173" s="12">
+        <v>3.6218530100000002</v>
+      </c>
+      <c r="M173" s="13">
+        <v>2.3561509300000001</v>
+      </c>
+    </row>
+    <row r="174" spans="1:13">
       <c r="A174">
         <v>20224</v>
       </c>
@@ -6741,7 +8252,7 @@
       <c r="F174" s="8">
         <v>82.787000000000006</v>
       </c>
-      <c r="G174" s="9">
+      <c r="G174" s="7">
         <v>7.1</v>
       </c>
       <c r="H174" s="2">
@@ -6750,11 +8261,20 @@
       <c r="I174" s="2">
         <v>4.8</v>
       </c>
-      <c r="J174" s="10">
+      <c r="J174" s="9">
         <v>2.9611999999999998</v>
       </c>
-    </row>
-    <row r="175" spans="1:10">
+      <c r="K174" s="10">
+        <v>2.34828554</v>
+      </c>
+      <c r="L174" s="12">
+        <v>2.9963756300000002</v>
+      </c>
+      <c r="M174" s="13">
+        <v>2.44991067</v>
+      </c>
+    </row>
+    <row r="175" spans="1:13">
       <c r="A175">
         <v>20231</v>
       </c>
@@ -6773,7 +8293,7 @@
       <c r="F175" s="8">
         <v>76.076999999999998</v>
       </c>
-      <c r="G175" s="9">
+      <c r="G175" s="7">
         <v>5.7</v>
       </c>
       <c r="H175" s="2">
@@ -6782,11 +8302,20 @@
       <c r="I175" s="2">
         <v>3.9</v>
       </c>
-      <c r="J175" s="10">
+      <c r="J175" s="9">
         <v>2.6903000000000001</v>
       </c>
-    </row>
-    <row r="176" spans="1:10">
+      <c r="K175" s="10">
+        <v>2.2166576099999999</v>
+      </c>
+      <c r="L175" s="12">
+        <v>2.4551188100000001</v>
+      </c>
+      <c r="M175" s="13">
+        <v>2.3774331100000001</v>
+      </c>
+    </row>
+    <row r="176" spans="1:13">
       <c r="A176">
         <v>20232</v>
       </c>
@@ -6805,7 +8334,7 @@
       <c r="F176" s="8">
         <v>73.760000000000005</v>
       </c>
-      <c r="G176" s="9">
+      <c r="G176" s="7">
         <v>4</v>
       </c>
       <c r="H176" s="2">
@@ -6814,11 +8343,20 @@
       <c r="I176" s="2">
         <v>4.0999999999999996</v>
       </c>
-      <c r="J176" s="10">
+      <c r="J176" s="9">
         <v>2.5348999999999999</v>
       </c>
-    </row>
-    <row r="177" spans="1:10">
+      <c r="K176" s="10">
+        <v>2.00706652</v>
+      </c>
+      <c r="L176" s="12">
+        <v>2.2235778900000001</v>
+      </c>
+      <c r="M176" s="13">
+        <v>2.24664273</v>
+      </c>
+    </row>
+    <row r="177" spans="1:13">
       <c r="A177">
         <v>20233</v>
       </c>
@@ -6837,7 +8375,7 @@
       <c r="F177" s="8">
         <v>82.296999999999997</v>
       </c>
-      <c r="G177" s="9">
+      <c r="G177" s="7">
         <v>3.6</v>
       </c>
       <c r="H177" s="2">
@@ -6846,11 +8384,20 @@
       <c r="I177" s="2">
         <v>3.4</v>
       </c>
-      <c r="J177" s="10">
+      <c r="J177" s="9">
         <v>2.5076999999999998</v>
       </c>
-    </row>
-    <row r="178" spans="1:10">
+      <c r="K177" s="10">
+        <v>2.1416656199999999</v>
+      </c>
+      <c r="L177" s="12">
+        <v>2.6312400999999999</v>
+      </c>
+      <c r="M177" s="13">
+        <v>2.3184391600000001</v>
+      </c>
+    </row>
+    <row r="178" spans="1:13">
       <c r="A178">
         <v>20234</v>
       </c>
@@ -6869,7 +8416,7 @@
       <c r="F178" s="8">
         <v>78.41</v>
       </c>
-      <c r="G178" s="9">
+      <c r="G178" s="7">
         <v>3.2</v>
       </c>
       <c r="H178" s="2">
@@ -6878,11 +8425,20 @@
       <c r="I178" s="2">
         <v>3.9</v>
       </c>
-      <c r="J178" s="10">
+      <c r="J178" s="9">
         <v>2.2604000000000002</v>
       </c>
-    </row>
-    <row r="179" spans="1:10">
+      <c r="K178" s="10">
+        <v>2.3417291100000002</v>
+      </c>
+      <c r="L178" s="12">
+        <v>2.8841447900000001</v>
+      </c>
+      <c r="M178" s="13">
+        <v>2.44121144</v>
+      </c>
+    </row>
+    <row r="179" spans="1:13">
       <c r="A179">
         <v>20241</v>
       </c>
@@ -6901,7 +8457,7 @@
       <c r="F179" s="8">
         <v>77.56</v>
       </c>
-      <c r="G179" s="9">
+      <c r="G179" s="7">
         <v>3.2</v>
       </c>
       <c r="H179" s="2">
@@ -6910,11 +8466,20 @@
       <c r="I179" s="2">
         <v>2.9</v>
       </c>
-      <c r="J179" s="10">
+      <c r="J179" s="9">
         <v>2.1057999999999999</v>
       </c>
-    </row>
-    <row r="180" spans="1:10">
+      <c r="K179" s="10">
+        <v>2.17648698</v>
+      </c>
+      <c r="L179" s="12">
+        <v>2.3097246400000002</v>
+      </c>
+      <c r="M179" s="13">
+        <v>2.3525405099999999</v>
+      </c>
+    </row>
+    <row r="180" spans="1:13">
       <c r="A180">
         <v>20242</v>
       </c>
@@ -6933,7 +8498,7 @@
       <c r="F180" s="8">
         <v>81.712999999999994</v>
       </c>
-      <c r="G180" s="9">
+      <c r="G180" s="7">
         <v>3.2</v>
       </c>
       <c r="H180" s="2">
@@ -6942,11 +8507,20 @@
       <c r="I180" s="2">
         <v>3.2</v>
       </c>
-      <c r="J180" s="10">
+      <c r="J180" s="9">
         <v>2.1943999999999999</v>
       </c>
-    </row>
-    <row r="181" spans="1:10">
+      <c r="K180" s="10">
+        <v>2.3871753899999999</v>
+      </c>
+      <c r="L180" s="12">
+        <v>2.7886248999999999</v>
+      </c>
+      <c r="M180" s="13">
+        <v>2.4746446899999999</v>
+      </c>
+    </row>
+    <row r="181" spans="1:13">
       <c r="A181">
         <v>20243</v>
       </c>
@@ -6965,7 +8539,7 @@
       <c r="F181" s="8">
         <v>76.239999999999995</v>
       </c>
-      <c r="G181" s="9">
+      <c r="G181" s="7">
         <v>2.7</v>
       </c>
       <c r="H181" s="2">
@@ -6974,11 +8548,20 @@
       <c r="I181" s="2">
         <v>2.8</v>
       </c>
-      <c r="J181" s="10">
+      <c r="J181" s="9">
         <v>2.1438999999999999</v>
       </c>
-    </row>
-    <row r="182" spans="1:10">
+      <c r="K181" s="10">
+        <v>2.2189204500000002</v>
+      </c>
+      <c r="L181" s="12">
+        <v>2.3796082099999998</v>
+      </c>
+      <c r="M181" s="13">
+        <v>2.3782587400000001</v>
+      </c>
+    </row>
+    <row r="182" spans="1:13">
       <c r="A182">
         <v>20244</v>
       </c>
@@ -6997,7 +8580,7 @@
       <c r="F182" s="8">
         <v>70.686999999999998</v>
       </c>
-      <c r="G182" s="9">
+      <c r="G182" s="7">
         <v>2.7</v>
       </c>
       <c r="H182" s="2">
@@ -7006,11 +8589,20 @@
       <c r="I182" s="2">
         <v>2.7</v>
       </c>
-      <c r="J182" s="10">
+      <c r="J182" s="9">
         <v>2.2161</v>
       </c>
-    </row>
-    <row r="183" spans="1:10">
+      <c r="K182" s="10">
+        <v>2.2576411200000002</v>
+      </c>
+      <c r="L182" s="12">
+        <v>2.44605352</v>
+      </c>
+      <c r="M182" s="13">
+        <v>2.4051565500000001</v>
+      </c>
+    </row>
+    <row r="183" spans="1:13">
       <c r="A183">
         <v>20251</v>
       </c>
@@ -7029,7 +8621,7 @@
       <c r="F183" s="8">
         <v>71.837000000000003</v>
       </c>
-      <c r="G183" s="9">
+      <c r="G183" s="7">
         <v>2.7</v>
       </c>
       <c r="H183" s="2">
@@ -7038,11 +8630,20 @@
       <c r="I183" s="2">
         <v>4.2</v>
       </c>
-      <c r="J183" s="10">
+      <c r="J183" s="9">
         <v>2.5430999999999999</v>
       </c>
-    </row>
-    <row r="184" spans="1:10">
+      <c r="K183" s="10">
+        <v>2.4025278499999998</v>
+      </c>
+      <c r="L183" s="12">
+        <v>2.5128244500000001</v>
+      </c>
+      <c r="M183" s="13">
+        <v>2.4999204599999998</v>
+      </c>
+    </row>
+    <row r="184" spans="1:13">
       <c r="A184">
         <v>20252</v>
       </c>
@@ -7061,7 +8662,7 @@
       <c r="F184" s="8">
         <v>64.626999999999995</v>
       </c>
-      <c r="G184" s="9">
+      <c r="G184" s="7">
         <v>2.5</v>
       </c>
       <c r="H184" s="2">
@@ -7070,15 +8671,24 @@
       <c r="I184" s="2">
         <v>6</v>
       </c>
-      <c r="J184" s="10">
+      <c r="J184" s="9">
         <v>2.8119999999999998</v>
       </c>
-    </row>
-    <row r="185" spans="1:10">
-      <c r="J185" s="10"/>
+      <c r="K184" s="10">
+        <v>2.3357519299999998</v>
+      </c>
+      <c r="L184" s="12">
+        <v>2.65302163</v>
+      </c>
+      <c r="M184" s="13">
+        <v>2.45120548</v>
+      </c>
+    </row>
+    <row r="185" spans="1:13">
+      <c r="J185" s="9"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
